--- a/excel/Profitus Rima.xlsx
+++ b/excel/Profitus Rima.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.06.03\Profitus\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Investavimas 2026.06.03\Profitus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6537DDA4-E4A0-450B-AE4A-FC0F21E24240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5114DB5D-8F19-4CA2-8665-6B9FC1EE7D73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -244,7 +244,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="yyyy\.mm\.dd;@"/>
-    <numFmt numFmtId="167" formatCode="yyyy/mm/dd;@"/>
+    <numFmt numFmtId="166" formatCode="yyyy/mm/dd;@"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -385,7 +385,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -425,7 +425,7 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -436,9 +436,6 @@
     <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -446,9 +443,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -480,95 +474,11 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="68">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="31">
     <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -624,21 +534,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -694,63 +590,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -806,41 +646,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
@@ -863,76 +668,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1724,111 +1459,111 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="29" t="s">
+      <c r="A1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="O1" s="29" t="s">
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="O1" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="29"/>
-      <c r="S1" s="29" t="s">
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="T1" s="29"/>
-      <c r="U1" s="30" t="s">
+      <c r="T1" s="27"/>
+      <c r="U1" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="30"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
     </row>
     <row r="2" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="E2" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="G2" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="J2" s="23" t="s">
+      <c r="J2" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="K2" s="23" t="s">
+      <c r="K2" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="M2" s="25" t="s">
+      <c r="L2" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="M2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="O2" s="25" t="s">
+      <c r="O2" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="P2" s="25" t="s">
+      <c r="P2" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="Q2" s="25" t="s">
+      <c r="Q2" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="25" t="s">
+      <c r="R2" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="S2" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="T2" s="25" t="s">
+      <c r="S2" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="T2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="U2" s="25" t="s">
+      <c r="U2" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="V2" s="25" t="s">
+      <c r="V2" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="W2" s="25" t="s">
+      <c r="W2" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="X2" s="25" t="s">
+      <c r="X2" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="AC2" s="24" t="s">
+      <c r="AC2" s="7" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1870,7 +1605,7 @@
       </c>
       <c r="J3" s="9">
         <f ca="1">'Senvagės loftai, Panevėžys IV'!B13</f>
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K3" s="9" t="str">
         <f ca="1">'Senvagės loftai, Panevėžys IV'!S3</f>
@@ -1922,7 +1657,7 @@
       </c>
       <c r="X3" s="14">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.13741428256034854</v>
+        <v>0.13586096167564396</v>
       </c>
       <c r="AC3" s="9" t="str">
         <f ca="1">'Senvagės loftai, Panevėžys IV'!AA2</f>
@@ -2024,11 +1759,11 @@
       </c>
       <c r="J5" s="9">
         <f ca="1">'Butai centrinėje Vilniaus dal.'!B13</f>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K5" s="9">
         <f ca="1">'Butai centrinėje Vilniaus dal.'!S3</f>
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L5" s="5">
         <f>'Butai centrinėje Vilniaus dal.'!N3</f>
@@ -2081,7 +1816,7 @@
       </c>
       <c r="J6" s="9">
         <f ca="1">'Butas Didlaukio g., Vilnius II'!B13</f>
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="K6" s="9" t="str">
         <f ca="1">'Butas Didlaukio g., Vilnius II'!S3</f>
@@ -2096,7 +1831,7 @@
         <v>0</v>
       </c>
       <c r="AC6" s="9" t="str">
-        <f ca="1">'[1]Elfa loftai II'!AA2</f>
+        <f>'[1]Elfa loftai II'!AA2</f>
         <v/>
       </c>
     </row>
@@ -2138,7 +1873,7 @@
       </c>
       <c r="J7" s="9">
         <f ca="1">'Daugiabutis Druskininkuose V'!B13</f>
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="K7" s="9" t="str">
         <f ca="1">'Daugiabutis Druskininkuose V'!S3</f>
@@ -2153,7 +1888,7 @@
         <v>0</v>
       </c>
       <c r="AC7" s="9" t="str">
-        <f ca="1">'[1]Kęstučio salos'!AA2</f>
+        <f>'[1]Kęstučio salos'!AA2</f>
         <v/>
       </c>
     </row>
@@ -2195,7 +1930,7 @@
       </c>
       <c r="J8" s="9">
         <f ca="1">'Druskonio Perlai, Druskininkai '!B13</f>
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="K8" s="9" t="str">
         <f ca="1">'Druskonio Perlai, Druskininkai '!S3</f>
@@ -2210,7 +1945,7 @@
         <v>0</v>
       </c>
       <c r="AC8" s="9" t="str">
-        <f ca="1">'[1]Twinhouse XIII'!AA2</f>
+        <f>'[1]Twinhouse XIII'!AA2</f>
         <v/>
       </c>
     </row>
@@ -2231,7 +1966,7 @@
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="AC9" s="9" t="str">
-        <f ca="1">'[1]Vyčio slėnis VIII'!AA2</f>
+        <f>'[1]Vyčio slėnis VIII'!AA2</f>
         <v/>
       </c>
     </row>
@@ -2252,7 +1987,7 @@
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="AC10" s="9" t="str">
-        <f ca="1">'[1]Dvibutis Upės g.'!AA2</f>
+        <f>'[1]Dvibutis Upės g.'!AA2</f>
         <v/>
       </c>
     </row>
@@ -2273,7 +2008,7 @@
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="AC11" s="9" t="str">
-        <f ca="1">'[1]Dvibutis Klevų g.'!AA2</f>
+        <f>'[1]Dvibutis Klevų g.'!AA2</f>
         <v/>
       </c>
     </row>
@@ -2294,7 +2029,7 @@
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
       <c r="AC12" s="9" t="str">
-        <f ca="1">'[1]Dvibutis Upelio g., Vilniaus r.'!AA2</f>
+        <f>'[1]Dvibutis Upelio g., Vilniaus r.'!AA2</f>
         <v/>
       </c>
     </row>
@@ -2315,7 +2050,7 @@
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
       <c r="AC13" s="9" t="str">
-        <f ca="1">'[1]Piekrasta Rezidence, Ryga XII'!AA2</f>
+        <f>'[1]Piekrasta Rezidence, Ryga XII'!AA2</f>
         <v/>
       </c>
     </row>
@@ -2336,7 +2071,7 @@
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
       <c r="AC14" s="9" t="str">
-        <f ca="1">'[1]Dvibutis Didžiojoje Riešėje'!AA2</f>
+        <f>'[1]Dvibutis Didžiojoje Riešėje'!AA2</f>
         <v/>
       </c>
     </row>
@@ -2357,7 +2092,7 @@
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
       <c r="AC15" s="9" t="str">
-        <f ca="1">'[1]Sklypas Kalnėnuose, Vilnius II'!AA2</f>
+        <f>'[1]Sklypas Kalnėnuose, Vilnius II'!AA2</f>
         <v/>
       </c>
     </row>
@@ -2378,7 +2113,7 @@
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
       <c r="AC16" s="9" t="str">
-        <f ca="1">'[1]Golf Hills Vilos, Alikantė'!AA2</f>
+        <f>'[1]Golf Hills Vilos, Alikantė'!AA2</f>
         <v/>
       </c>
     </row>
@@ -2399,7 +2134,7 @@
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="AC17" s="9" t="str">
-        <f ca="1">'[1]Svajonių Daugiabutis, Kaunas'!AA2</f>
+        <f>'[1]Svajonių Daugiabutis, Kaunas'!AA2</f>
         <v/>
       </c>
     </row>
@@ -2420,7 +2155,7 @@
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="AC18" s="9" t="str">
-        <f ca="1">'[1]Brivibas 28, Jūrmala'!AA2</f>
+        <f>'[1]Brivibas 28, Jūrmala'!AA2</f>
         <v/>
       </c>
     </row>
@@ -2459,7 +2194,7 @@
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
       <c r="AC20" s="5" t="str">
-        <f ca="1">'[1]Molėtų Oazė XII'!AA2</f>
+        <f>'[1]Molėtų Oazė XII'!AA2</f>
         <v/>
       </c>
     </row>
@@ -2588,36 +2323,35 @@
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="U1:X1"/>
   </mergeCells>
-  <conditionalFormatting sqref="AC20">
-    <cfRule type="expression" dxfId="8" priority="7">
-      <formula>AND($G20&gt;0,$G20=$L20)</formula>
+  <conditionalFormatting sqref="A3:M27">
+    <cfRule type="expression" dxfId="30" priority="1">
+      <formula>$AC3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="8">
-      <formula>$AC20="+"</formula>
+    <cfRule type="expression" dxfId="29" priority="2">
+      <formula>AND($G3&gt;0,$G3=$L3)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC4">
-    <cfRule type="expression" dxfId="6" priority="5">
-      <formula>AND($G4&gt;0,$G4=$L4)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="6">
+    <cfRule type="expression" dxfId="28" priority="6">
       <formula>$AC$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AC4:AC5">
+    <cfRule type="expression" dxfId="27" priority="3">
+      <formula>AND($G4&gt;0,$G4=$L4)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AC5">
-    <cfRule type="expression" dxfId="4" priority="3">
-      <formula>AND($G5&gt;0,$G5=$L5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="26" priority="4">
       <formula>#REF!="+"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:M27">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>$AC3="+"</formula>
+  <conditionalFormatting sqref="AC20">
+    <cfRule type="expression" dxfId="25" priority="7">
+      <formula>AND($G20&gt;0,$G20=$L20)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
-      <formula>AND($G3&gt;0,$G3=$L3)</formula>
+    <cfRule type="expression" dxfId="24" priority="8">
+      <formula>$AC20="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -2638,7 +2372,7 @@
   <dimension ref="A1:L200"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" style="21" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" style="20" customWidth="1"/>
     <col min="2" max="4" width="10.7109375" customWidth="1"/>
     <col min="5" max="5" width="8.7109375" customWidth="1"/>
     <col min="6" max="9" width="10.7109375" customWidth="1"/>
@@ -2671,12 +2405,12 @@
       <c r="I1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="20" t="s">
+      <c r="K1" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="22">
+      <c r="L1" s="21">
         <f ca="1">XIRR(K2:K200,A2:A200)</f>
-        <v>0.13741428256034854</v>
+        <v>0.13586096167564396</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -4142,7 +3876,7 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="10">
         <f ca="1">TODAY()</f>
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -4183,22 +3917,22 @@
       <c r="B1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="24" t="s">
+      <c r="E1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="24" t="s">
+      <c r="G1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="I1" s="7" t="s">
         <v>36</v>
       </c>
       <c r="J1" s="11" t="s">
@@ -4207,30 +3941,30 @@
       <c r="K1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="28"/>
-      <c r="O1" s="26" t="s">
+      <c r="M1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="26"/>
+      <c r="O1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="31" t="s">
+      <c r="P1" s="26"/>
+      <c r="Q1" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="29" t="s">
         <v>47</v>
       </c>
       <c r="Y1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="Z1" s="24" t="s">
+      <c r="Z1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="AA1" s="24" t="s">
+      <c r="AA1" s="7" t="s">
         <v>47</v>
       </c>
     </row>
@@ -4264,15 +3998,15 @@
       <c r="N2" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="O2" s="24" t="s">
+      <c r="O2" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="P2" s="24" t="s">
+      <c r="P2" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
       <c r="Y2" s="10">
         <f>B3</f>
         <v>46191</v>
@@ -4608,7 +4342,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="5"/>
@@ -4635,7 +4369,7 @@
         <v>23</v>
       </c>
       <c r="B14" s="10"/>
-      <c r="D14" s="24"/>
+      <c r="D14" s="7"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
@@ -4663,7 +4397,7 @@
         <f>IF(M3=N3,B14-B12,"")</f>
         <v/>
       </c>
-      <c r="D15" s="24"/>
+      <c r="D15" s="7"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
@@ -4684,7 +4418,7 @@
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D16" s="24"/>
+      <c r="D16" s="7"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -4705,7 +4439,7 @@
       </c>
     </row>
     <row r="17" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D17" s="24"/>
+      <c r="D17" s="7"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -4726,7 +4460,7 @@
       </c>
     </row>
     <row r="18" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D18" s="24"/>
+      <c r="D18" s="7"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
@@ -4747,7 +4481,7 @@
       </c>
     </row>
     <row r="19" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D19" s="24"/>
+      <c r="D19" s="7"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
@@ -4768,7 +4502,7 @@
       </c>
     </row>
     <row r="20" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D20" s="24"/>
+      <c r="D20" s="7"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -4789,7 +4523,7 @@
       </c>
     </row>
     <row r="21" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D21" s="24"/>
+      <c r="D21" s="7"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
@@ -4810,7 +4544,7 @@
       </c>
     </row>
     <row r="22" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D22" s="24"/>
+      <c r="D22" s="7"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
@@ -4831,7 +4565,7 @@
       </c>
     </row>
     <row r="23" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D23" s="24"/>
+      <c r="D23" s="7"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
@@ -4852,7 +4586,7 @@
       </c>
     </row>
     <row r="24" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D24" s="24"/>
+      <c r="D24" s="7"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
@@ -4873,7 +4607,7 @@
       </c>
     </row>
     <row r="25" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D25" s="24"/>
+      <c r="D25" s="7"/>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
@@ -4894,7 +4628,7 @@
       </c>
     </row>
     <row r="26" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D26" s="24"/>
+      <c r="D26" s="7"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
@@ -4915,7 +4649,7 @@
       </c>
     </row>
     <row r="27" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D27" s="24"/>
+      <c r="D27" s="7"/>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
@@ -4936,7 +4670,7 @@
       </c>
     </row>
     <row r="28" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D28" s="24"/>
+      <c r="D28" s="7"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -4957,7 +4691,7 @@
       </c>
     </row>
     <row r="29" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D29" s="24"/>
+      <c r="D29" s="7"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -4978,7 +4712,7 @@
       </c>
     </row>
     <row r="30" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D30" s="24"/>
+      <c r="D30" s="7"/>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
@@ -4999,7 +4733,7 @@
       </c>
     </row>
     <row r="31" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D31" s="24"/>
+      <c r="D31" s="7"/>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
@@ -5020,7 +4754,7 @@
       </c>
     </row>
     <row r="32" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D32" s="24"/>
+      <c r="D32" s="7"/>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
@@ -5041,7 +4775,7 @@
       </c>
     </row>
     <row r="33" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D33" s="24"/>
+      <c r="D33" s="7"/>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
@@ -5062,7 +4796,7 @@
       </c>
     </row>
     <row r="34" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D34" s="24"/>
+      <c r="D34" s="7"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
@@ -5083,7 +4817,7 @@
       </c>
     </row>
     <row r="35" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D35" s="24"/>
+      <c r="D35" s="7"/>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
@@ -5104,7 +4838,7 @@
       </c>
     </row>
     <row r="36" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D36" s="24"/>
+      <c r="D36" s="7"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
@@ -5125,7 +4859,7 @@
       </c>
     </row>
     <row r="37" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D37" s="24"/>
+      <c r="D37" s="7"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
@@ -5146,7 +4880,7 @@
       </c>
     </row>
     <row r="38" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D38" s="24"/>
+      <c r="D38" s="7"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -5167,7 +4901,7 @@
       </c>
     </row>
     <row r="39" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D39" s="24"/>
+      <c r="D39" s="7"/>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
@@ -5188,7 +4922,7 @@
       </c>
     </row>
     <row r="40" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D40" s="24"/>
+      <c r="D40" s="7"/>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
@@ -5209,7 +4943,7 @@
       </c>
     </row>
     <row r="41" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D41" s="24"/>
+      <c r="D41" s="7"/>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
@@ -5230,7 +4964,7 @@
       </c>
     </row>
     <row r="42" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D42" s="24" t="s">
+      <c r="D42" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E42" s="5">
@@ -5264,22 +4998,22 @@
     <mergeCell ref="R1:R2"/>
     <mergeCell ref="S1:S2"/>
   </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="23" priority="1">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="2">
+      <formula>$M$3=$N$3</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="S3">
-    <cfRule type="expression" dxfId="17" priority="7">
+    <cfRule type="expression" dxfId="21" priority="7">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2">
-    <cfRule type="expression" dxfId="16" priority="8">
+    <cfRule type="expression" dxfId="20" priority="8">
       <formula>$AA$2="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="11" priority="1">
-      <formula>$AA$2="+"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="2">
-      <formula>$M$3=$N$3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5312,22 +5046,22 @@
       <c r="B1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="24" t="s">
+      <c r="E1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="24" t="s">
+      <c r="G1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="I1" s="7" t="s">
         <v>36</v>
       </c>
       <c r="J1" s="11" t="s">
@@ -5336,30 +5070,30 @@
       <c r="K1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="28"/>
-      <c r="O1" s="26" t="s">
+      <c r="M1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="26"/>
+      <c r="O1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="31" t="s">
+      <c r="P1" s="26"/>
+      <c r="Q1" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="29" t="s">
         <v>47</v>
       </c>
       <c r="Y1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="Z1" s="24" t="s">
+      <c r="Z1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="AA1" s="24" t="s">
+      <c r="AA1" s="7" t="s">
         <v>47</v>
       </c>
     </row>
@@ -5393,15 +5127,15 @@
       <c r="N2" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="O2" s="24" t="s">
+      <c r="O2" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="P2" s="24" t="s">
+      <c r="P2" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
       <c r="Y2" s="10">
         <f>B3</f>
         <v>46161</v>
@@ -5737,7 +5471,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="5"/>
@@ -5764,7 +5498,7 @@
         <v>23</v>
       </c>
       <c r="B14" s="10"/>
-      <c r="D14" s="24"/>
+      <c r="D14" s="7"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
@@ -5792,7 +5526,7 @@
         <f>IF(M3=N3,B14-B12,"")</f>
         <v/>
       </c>
-      <c r="D15" s="24"/>
+      <c r="D15" s="7"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
@@ -5813,7 +5547,7 @@
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D16" s="24"/>
+      <c r="D16" s="7"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -5834,7 +5568,7 @@
       </c>
     </row>
     <row r="17" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D17" s="24"/>
+      <c r="D17" s="7"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -5855,7 +5589,7 @@
       </c>
     </row>
     <row r="18" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D18" s="24"/>
+      <c r="D18" s="7"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
@@ -5876,7 +5610,7 @@
       </c>
     </row>
     <row r="19" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D19" s="24"/>
+      <c r="D19" s="7"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
@@ -5897,7 +5631,7 @@
       </c>
     </row>
     <row r="20" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D20" s="24"/>
+      <c r="D20" s="7"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -5918,7 +5652,7 @@
       </c>
     </row>
     <row r="21" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D21" s="24"/>
+      <c r="D21" s="7"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
@@ -5939,7 +5673,7 @@
       </c>
     </row>
     <row r="22" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D22" s="24"/>
+      <c r="D22" s="7"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
@@ -5960,7 +5694,7 @@
       </c>
     </row>
     <row r="23" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D23" s="24"/>
+      <c r="D23" s="7"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
@@ -5981,7 +5715,7 @@
       </c>
     </row>
     <row r="24" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D24" s="24"/>
+      <c r="D24" s="7"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
@@ -6002,7 +5736,7 @@
       </c>
     </row>
     <row r="25" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D25" s="24"/>
+      <c r="D25" s="7"/>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
@@ -6023,7 +5757,7 @@
       </c>
     </row>
     <row r="26" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D26" s="24"/>
+      <c r="D26" s="7"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
@@ -6044,7 +5778,7 @@
       </c>
     </row>
     <row r="27" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D27" s="24"/>
+      <c r="D27" s="7"/>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
@@ -6065,7 +5799,7 @@
       </c>
     </row>
     <row r="28" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D28" s="24"/>
+      <c r="D28" s="7"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -6086,7 +5820,7 @@
       </c>
     </row>
     <row r="29" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D29" s="24"/>
+      <c r="D29" s="7"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -6107,7 +5841,7 @@
       </c>
     </row>
     <row r="30" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D30" s="24"/>
+      <c r="D30" s="7"/>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
@@ -6128,7 +5862,7 @@
       </c>
     </row>
     <row r="31" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D31" s="24"/>
+      <c r="D31" s="7"/>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
@@ -6149,7 +5883,7 @@
       </c>
     </row>
     <row r="32" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D32" s="24"/>
+      <c r="D32" s="7"/>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
@@ -6170,7 +5904,7 @@
       </c>
     </row>
     <row r="33" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D33" s="24"/>
+      <c r="D33" s="7"/>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
@@ -6191,7 +5925,7 @@
       </c>
     </row>
     <row r="34" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D34" s="24"/>
+      <c r="D34" s="7"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
@@ -6212,7 +5946,7 @@
       </c>
     </row>
     <row r="35" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D35" s="24"/>
+      <c r="D35" s="7"/>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
@@ -6233,7 +5967,7 @@
       </c>
     </row>
     <row r="36" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D36" s="24"/>
+      <c r="D36" s="7"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
@@ -6254,7 +5988,7 @@
       </c>
     </row>
     <row r="37" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D37" s="24"/>
+      <c r="D37" s="7"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
@@ -6275,7 +6009,7 @@
       </c>
     </row>
     <row r="38" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D38" s="24"/>
+      <c r="D38" s="7"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -6296,7 +6030,7 @@
       </c>
     </row>
     <row r="39" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D39" s="24"/>
+      <c r="D39" s="7"/>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
@@ -6317,7 +6051,7 @@
       </c>
     </row>
     <row r="40" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D40" s="24"/>
+      <c r="D40" s="7"/>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
@@ -6338,7 +6072,7 @@
       </c>
     </row>
     <row r="41" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D41" s="24"/>
+      <c r="D41" s="7"/>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
@@ -6359,7 +6093,7 @@
       </c>
     </row>
     <row r="42" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D42" s="24" t="s">
+      <c r="D42" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E42" s="5">
@@ -6393,22 +6127,22 @@
     <mergeCell ref="R1:R2"/>
     <mergeCell ref="S1:S2"/>
   </mergeCells>
-  <conditionalFormatting sqref="S3">
-    <cfRule type="expression" dxfId="27" priority="7">
-      <formula>$AA$2="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA2">
-    <cfRule type="expression" dxfId="26" priority="8">
-      <formula>$AA$2="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
     <cfRule type="expression" dxfId="19" priority="1">
       <formula>$AA$2="+"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="18" priority="2">
       <formula>$M$3=$N$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S3">
+    <cfRule type="expression" dxfId="17" priority="7">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2">
+    <cfRule type="expression" dxfId="16" priority="8">
+      <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6441,22 +6175,22 @@
       <c r="B1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="24" t="s">
+      <c r="E1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="24" t="s">
+      <c r="G1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="I1" s="7" t="s">
         <v>36</v>
       </c>
       <c r="J1" s="11" t="s">
@@ -6465,30 +6199,30 @@
       <c r="K1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="28"/>
-      <c r="O1" s="26" t="s">
+      <c r="M1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="26"/>
+      <c r="O1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="31" t="s">
+      <c r="P1" s="26"/>
+      <c r="Q1" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="29" t="s">
         <v>47</v>
       </c>
       <c r="Y1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="Z1" s="24" t="s">
+      <c r="Z1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="AA1" s="24" t="s">
+      <c r="AA1" s="7" t="s">
         <v>47</v>
       </c>
     </row>
@@ -6522,15 +6256,15 @@
       <c r="N2" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="O2" s="24" t="s">
+      <c r="O2" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="P2" s="24" t="s">
+      <c r="P2" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
       <c r="Y2" s="10">
         <f>B3</f>
         <v>46157</v>
@@ -6866,7 +6600,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="5"/>
@@ -6893,7 +6627,7 @@
         <v>23</v>
       </c>
       <c r="B14" s="10"/>
-      <c r="D14" s="24"/>
+      <c r="D14" s="7"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
@@ -6921,7 +6655,7 @@
         <f>IF(M3=N3,B14-B12,"")</f>
         <v/>
       </c>
-      <c r="D15" s="24"/>
+      <c r="D15" s="7"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
@@ -6942,7 +6676,7 @@
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D16" s="24"/>
+      <c r="D16" s="7"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -6963,7 +6697,7 @@
       </c>
     </row>
     <row r="17" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D17" s="24"/>
+      <c r="D17" s="7"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -6984,7 +6718,7 @@
       </c>
     </row>
     <row r="18" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D18" s="24"/>
+      <c r="D18" s="7"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
@@ -7005,7 +6739,7 @@
       </c>
     </row>
     <row r="19" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D19" s="24"/>
+      <c r="D19" s="7"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
@@ -7026,7 +6760,7 @@
       </c>
     </row>
     <row r="20" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D20" s="24"/>
+      <c r="D20" s="7"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -7047,7 +6781,7 @@
       </c>
     </row>
     <row r="21" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D21" s="24"/>
+      <c r="D21" s="7"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
@@ -7068,7 +6802,7 @@
       </c>
     </row>
     <row r="22" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D22" s="24"/>
+      <c r="D22" s="7"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
@@ -7089,7 +6823,7 @@
       </c>
     </row>
     <row r="23" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D23" s="24"/>
+      <c r="D23" s="7"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
@@ -7110,7 +6844,7 @@
       </c>
     </row>
     <row r="24" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D24" s="24"/>
+      <c r="D24" s="7"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
@@ -7131,7 +6865,7 @@
       </c>
     </row>
     <row r="25" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D25" s="24"/>
+      <c r="D25" s="7"/>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
@@ -7152,7 +6886,7 @@
       </c>
     </row>
     <row r="26" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D26" s="24"/>
+      <c r="D26" s="7"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
@@ -7173,7 +6907,7 @@
       </c>
     </row>
     <row r="27" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D27" s="24"/>
+      <c r="D27" s="7"/>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
@@ -7194,7 +6928,7 @@
       </c>
     </row>
     <row r="28" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D28" s="24"/>
+      <c r="D28" s="7"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -7215,7 +6949,7 @@
       </c>
     </row>
     <row r="29" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D29" s="24"/>
+      <c r="D29" s="7"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -7236,7 +6970,7 @@
       </c>
     </row>
     <row r="30" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D30" s="24"/>
+      <c r="D30" s="7"/>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
@@ -7257,7 +6991,7 @@
       </c>
     </row>
     <row r="31" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D31" s="24"/>
+      <c r="D31" s="7"/>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
@@ -7278,7 +7012,7 @@
       </c>
     </row>
     <row r="32" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D32" s="24"/>
+      <c r="D32" s="7"/>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
@@ -7299,7 +7033,7 @@
       </c>
     </row>
     <row r="33" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D33" s="24"/>
+      <c r="D33" s="7"/>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
@@ -7320,7 +7054,7 @@
       </c>
     </row>
     <row r="34" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D34" s="24"/>
+      <c r="D34" s="7"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
@@ -7341,7 +7075,7 @@
       </c>
     </row>
     <row r="35" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D35" s="24"/>
+      <c r="D35" s="7"/>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
@@ -7362,7 +7096,7 @@
       </c>
     </row>
     <row r="36" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D36" s="24"/>
+      <c r="D36" s="7"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
@@ -7383,7 +7117,7 @@
       </c>
     </row>
     <row r="37" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D37" s="24"/>
+      <c r="D37" s="7"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
@@ -7404,7 +7138,7 @@
       </c>
     </row>
     <row r="38" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D38" s="24"/>
+      <c r="D38" s="7"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -7425,7 +7159,7 @@
       </c>
     </row>
     <row r="39" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D39" s="24"/>
+      <c r="D39" s="7"/>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
@@ -7446,7 +7180,7 @@
       </c>
     </row>
     <row r="40" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D40" s="24"/>
+      <c r="D40" s="7"/>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
@@ -7467,7 +7201,7 @@
       </c>
     </row>
     <row r="41" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D41" s="24"/>
+      <c r="D41" s="7"/>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
@@ -7488,7 +7222,7 @@
       </c>
     </row>
     <row r="42" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D42" s="24" t="s">
+      <c r="D42" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E42" s="5">
@@ -7522,22 +7256,22 @@
     <mergeCell ref="R1:R2"/>
     <mergeCell ref="S1:S2"/>
   </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="15" priority="1">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="2">
+      <formula>$M$3=$N$3</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="S3">
-    <cfRule type="expression" dxfId="43" priority="11">
+    <cfRule type="expression" dxfId="13" priority="11">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2">
-    <cfRule type="expression" dxfId="42" priority="12">
+    <cfRule type="expression" dxfId="12" priority="12">
       <formula>$AA$2="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="21" priority="1">
-      <formula>$AA$2="+"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="20" priority="2">
-      <formula>$M$3=$N$3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7570,22 +7304,22 @@
       <c r="B1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="24" t="s">
+      <c r="E1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="24" t="s">
+      <c r="G1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="I1" s="7" t="s">
         <v>36</v>
       </c>
       <c r="J1" s="11" t="s">
@@ -7594,30 +7328,30 @@
       <c r="K1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="28"/>
-      <c r="O1" s="26" t="s">
+      <c r="M1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="26"/>
+      <c r="O1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="31" t="s">
+      <c r="P1" s="26"/>
+      <c r="Q1" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="29" t="s">
         <v>47</v>
       </c>
       <c r="Y1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="Z1" s="24" t="s">
+      <c r="Z1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="AA1" s="24" t="s">
+      <c r="AA1" s="7" t="s">
         <v>47</v>
       </c>
     </row>
@@ -7659,15 +7393,15 @@
       <c r="N2" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="O2" s="24" t="s">
+      <c r="O2" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="P2" s="24" t="s">
+      <c r="P2" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
       <c r="Y2" s="10">
         <f>B3</f>
         <v>45979</v>
@@ -7731,7 +7465,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Y3" s="10">
         <f>J2</f>
@@ -7997,7 +7731,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="5"/>
@@ -8024,7 +7758,7 @@
         <v>23</v>
       </c>
       <c r="B14" s="10"/>
-      <c r="D14" s="24"/>
+      <c r="D14" s="7"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
@@ -8052,7 +7786,7 @@
         <f>IF(M3=N3,B14-B12,"")</f>
         <v/>
       </c>
-      <c r="D15" s="24"/>
+      <c r="D15" s="7"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
@@ -8073,7 +7807,7 @@
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D16" s="24"/>
+      <c r="D16" s="7"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -8094,7 +7828,7 @@
       </c>
     </row>
     <row r="17" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D17" s="24"/>
+      <c r="D17" s="7"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -8115,7 +7849,7 @@
       </c>
     </row>
     <row r="18" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D18" s="24"/>
+      <c r="D18" s="7"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
@@ -8136,7 +7870,7 @@
       </c>
     </row>
     <row r="19" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D19" s="24"/>
+      <c r="D19" s="7"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
@@ -8157,7 +7891,7 @@
       </c>
     </row>
     <row r="20" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D20" s="24"/>
+      <c r="D20" s="7"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -8178,7 +7912,7 @@
       </c>
     </row>
     <row r="21" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D21" s="24"/>
+      <c r="D21" s="7"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
@@ -8199,7 +7933,7 @@
       </c>
     </row>
     <row r="22" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D22" s="24"/>
+      <c r="D22" s="7"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
@@ -8220,7 +7954,7 @@
       </c>
     </row>
     <row r="23" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D23" s="24"/>
+      <c r="D23" s="7"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
@@ -8241,7 +7975,7 @@
       </c>
     </row>
     <row r="24" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D24" s="24"/>
+      <c r="D24" s="7"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
@@ -8262,7 +7996,7 @@
       </c>
     </row>
     <row r="25" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D25" s="24"/>
+      <c r="D25" s="7"/>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
@@ -8283,7 +8017,7 @@
       </c>
     </row>
     <row r="26" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D26" s="24"/>
+      <c r="D26" s="7"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
@@ -8304,7 +8038,7 @@
       </c>
     </row>
     <row r="27" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D27" s="24"/>
+      <c r="D27" s="7"/>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
@@ -8325,7 +8059,7 @@
       </c>
     </row>
     <row r="28" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D28" s="24"/>
+      <c r="D28" s="7"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -8346,7 +8080,7 @@
       </c>
     </row>
     <row r="29" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D29" s="24"/>
+      <c r="D29" s="7"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -8367,7 +8101,7 @@
       </c>
     </row>
     <row r="30" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D30" s="24"/>
+      <c r="D30" s="7"/>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
@@ -8388,7 +8122,7 @@
       </c>
     </row>
     <row r="31" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D31" s="24"/>
+      <c r="D31" s="7"/>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
@@ -8409,7 +8143,7 @@
       </c>
     </row>
     <row r="32" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D32" s="24"/>
+      <c r="D32" s="7"/>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
@@ -8430,7 +8164,7 @@
       </c>
     </row>
     <row r="33" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D33" s="24"/>
+      <c r="D33" s="7"/>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
@@ -8451,7 +8185,7 @@
       </c>
     </row>
     <row r="34" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D34" s="24"/>
+      <c r="D34" s="7"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
@@ -8472,7 +8206,7 @@
       </c>
     </row>
     <row r="35" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D35" s="24"/>
+      <c r="D35" s="7"/>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
@@ -8493,7 +8227,7 @@
       </c>
     </row>
     <row r="36" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D36" s="24"/>
+      <c r="D36" s="7"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
@@ -8514,7 +8248,7 @@
       </c>
     </row>
     <row r="37" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D37" s="24"/>
+      <c r="D37" s="7"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
@@ -8535,7 +8269,7 @@
       </c>
     </row>
     <row r="38" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D38" s="24"/>
+      <c r="D38" s="7"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -8556,7 +8290,7 @@
       </c>
     </row>
     <row r="39" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D39" s="24"/>
+      <c r="D39" s="7"/>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
@@ -8577,7 +8311,7 @@
       </c>
     </row>
     <row r="40" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D40" s="24"/>
+      <c r="D40" s="7"/>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
@@ -8598,7 +8332,7 @@
       </c>
     </row>
     <row r="41" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D41" s="24"/>
+      <c r="D41" s="7"/>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
@@ -8619,7 +8353,7 @@
       </c>
     </row>
     <row r="42" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D42" s="24" t="s">
+      <c r="D42" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E42" s="5">
@@ -8653,22 +8387,22 @@
     <mergeCell ref="R1:R2"/>
     <mergeCell ref="S1:S2"/>
   </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="11" priority="1">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="2">
+      <formula>$M$3=$N$3</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="S3">
-    <cfRule type="expression" dxfId="51" priority="11">
+    <cfRule type="expression" dxfId="9" priority="11">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2">
-    <cfRule type="expression" dxfId="50" priority="12">
+    <cfRule type="expression" dxfId="8" priority="12">
       <formula>$AA$2="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="31" priority="1">
-      <formula>$AA$2="+"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="30" priority="2">
-      <formula>$M$3=$N$3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8704,22 +8438,22 @@
       <c r="B1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="24" t="s">
+      <c r="E1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="24" t="s">
+      <c r="G1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="I1" s="7" t="s">
         <v>36</v>
       </c>
       <c r="J1" s="11" t="s">
@@ -8728,30 +8462,30 @@
       <c r="K1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="28"/>
-      <c r="O1" s="26" t="s">
+      <c r="M1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="26"/>
+      <c r="O1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="31" t="s">
+      <c r="P1" s="26"/>
+      <c r="Q1" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="29" t="s">
         <v>47</v>
       </c>
       <c r="Y1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="Z1" s="24" t="s">
+      <c r="Z1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="AA1" s="24" t="s">
+      <c r="AA1" s="7" t="s">
         <v>47</v>
       </c>
     </row>
@@ -8793,15 +8527,15 @@
       <c r="N2" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="O2" s="24" t="s">
+      <c r="O2" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="P2" s="24" t="s">
+      <c r="P2" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
       <c r="Y2" s="10">
         <f>B3</f>
         <v>45899</v>
@@ -9190,7 +8924,7 @@
       <c r="B14" s="10">
         <v>46154</v>
       </c>
-      <c r="D14" s="24"/>
+      <c r="D14" s="7"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
@@ -9218,7 +8952,7 @@
         <f>IF(M3=N3,B14-B12,"")</f>
         <v>-111</v>
       </c>
-      <c r="D15" s="24"/>
+      <c r="D15" s="7"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
@@ -9239,7 +8973,7 @@
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D16" s="24"/>
+      <c r="D16" s="7"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -9260,7 +8994,7 @@
       </c>
     </row>
     <row r="17" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D17" s="24"/>
+      <c r="D17" s="7"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -9281,7 +9015,7 @@
       </c>
     </row>
     <row r="18" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D18" s="24"/>
+      <c r="D18" s="7"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
@@ -9302,7 +9036,7 @@
       </c>
     </row>
     <row r="19" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D19" s="24"/>
+      <c r="D19" s="7"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
@@ -9323,7 +9057,7 @@
       </c>
     </row>
     <row r="20" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D20" s="24"/>
+      <c r="D20" s="7"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -9344,7 +9078,7 @@
       </c>
     </row>
     <row r="21" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D21" s="24"/>
+      <c r="D21" s="7"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
@@ -9365,7 +9099,7 @@
       </c>
     </row>
     <row r="22" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D22" s="24"/>
+      <c r="D22" s="7"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
@@ -9386,7 +9120,7 @@
       </c>
     </row>
     <row r="23" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D23" s="24"/>
+      <c r="D23" s="7"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
@@ -9407,7 +9141,7 @@
       </c>
     </row>
     <row r="24" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D24" s="24"/>
+      <c r="D24" s="7"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
@@ -9428,7 +9162,7 @@
       </c>
     </row>
     <row r="25" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D25" s="24"/>
+      <c r="D25" s="7"/>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
@@ -9449,7 +9183,7 @@
       </c>
     </row>
     <row r="26" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D26" s="24"/>
+      <c r="D26" s="7"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
@@ -9470,7 +9204,7 @@
       </c>
     </row>
     <row r="27" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D27" s="24"/>
+      <c r="D27" s="7"/>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
@@ -9491,7 +9225,7 @@
       </c>
     </row>
     <row r="28" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D28" s="24"/>
+      <c r="D28" s="7"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -9512,7 +9246,7 @@
       </c>
     </row>
     <row r="29" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D29" s="24"/>
+      <c r="D29" s="7"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -9533,7 +9267,7 @@
       </c>
     </row>
     <row r="30" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D30" s="24"/>
+      <c r="D30" s="7"/>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
@@ -9554,7 +9288,7 @@
       </c>
     </row>
     <row r="31" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D31" s="24"/>
+      <c r="D31" s="7"/>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
@@ -9575,7 +9309,7 @@
       </c>
     </row>
     <row r="32" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D32" s="24"/>
+      <c r="D32" s="7"/>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
@@ -9596,7 +9330,7 @@
       </c>
     </row>
     <row r="33" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D33" s="24"/>
+      <c r="D33" s="7"/>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
@@ -9617,7 +9351,7 @@
       </c>
     </row>
     <row r="34" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D34" s="24"/>
+      <c r="D34" s="7"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
@@ -9638,7 +9372,7 @@
       </c>
     </row>
     <row r="35" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D35" s="24"/>
+      <c r="D35" s="7"/>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
@@ -9659,7 +9393,7 @@
       </c>
     </row>
     <row r="36" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D36" s="24"/>
+      <c r="D36" s="7"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
@@ -9680,7 +9414,7 @@
       </c>
     </row>
     <row r="37" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D37" s="24"/>
+      <c r="D37" s="7"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
@@ -9701,7 +9435,7 @@
       </c>
     </row>
     <row r="38" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D38" s="24"/>
+      <c r="D38" s="7"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -9722,7 +9456,7 @@
       </c>
     </row>
     <row r="39" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D39" s="24"/>
+      <c r="D39" s="7"/>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
@@ -9743,7 +9477,7 @@
       </c>
     </row>
     <row r="40" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D40" s="24"/>
+      <c r="D40" s="7"/>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
@@ -9764,7 +9498,7 @@
       </c>
     </row>
     <row r="41" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D41" s="24"/>
+      <c r="D41" s="7"/>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
@@ -9785,7 +9519,7 @@
       </c>
     </row>
     <row r="42" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D42" s="24" t="s">
+      <c r="D42" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E42" s="5">
@@ -9819,22 +9553,22 @@
     <mergeCell ref="R1:R2"/>
     <mergeCell ref="S1:S2"/>
   </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="7" priority="1">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="2">
+      <formula>$M$3=$N$3</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="S3">
-    <cfRule type="expression" dxfId="59" priority="9">
+    <cfRule type="expression" dxfId="5" priority="9">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2">
-    <cfRule type="expression" dxfId="58" priority="10">
+    <cfRule type="expression" dxfId="4" priority="10">
       <formula>$AA$2="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="35" priority="1">
-      <formula>$AA$2="+"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="2">
-      <formula>$M$3=$N$3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9867,22 +9601,22 @@
       <c r="B1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="24" t="s">
+      <c r="E1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="24" t="s">
+      <c r="G1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="I1" s="7" t="s">
         <v>36</v>
       </c>
       <c r="J1" s="11" t="s">
@@ -9891,30 +9625,30 @@
       <c r="K1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="28"/>
-      <c r="O1" s="26" t="s">
+      <c r="M1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="26"/>
+      <c r="O1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="31" t="s">
+      <c r="P1" s="26"/>
+      <c r="Q1" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="29" t="s">
         <v>47</v>
       </c>
       <c r="Y1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="Z1" s="24" t="s">
+      <c r="Z1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="AA1" s="24" t="s">
+      <c r="AA1" s="7" t="s">
         <v>47</v>
       </c>
     </row>
@@ -9956,15 +9690,15 @@
       <c r="N2" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="O2" s="24" t="s">
+      <c r="O2" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="P2" s="24" t="s">
+      <c r="P2" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
       <c r="Y2" s="10">
         <f>B3</f>
         <v>45899</v>
@@ -10316,7 +10050,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="5"/>
@@ -10343,7 +10077,7 @@
         <v>23</v>
       </c>
       <c r="B14" s="10"/>
-      <c r="D14" s="24"/>
+      <c r="D14" s="7"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
@@ -10371,7 +10105,7 @@
         <f>IF(M3=N3,B14-B12,"")</f>
         <v/>
       </c>
-      <c r="D15" s="24"/>
+      <c r="D15" s="7"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
@@ -10392,7 +10126,7 @@
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D16" s="24"/>
+      <c r="D16" s="7"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -10413,7 +10147,7 @@
       </c>
     </row>
     <row r="17" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D17" s="24"/>
+      <c r="D17" s="7"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -10434,7 +10168,7 @@
       </c>
     </row>
     <row r="18" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D18" s="24"/>
+      <c r="D18" s="7"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
@@ -10455,7 +10189,7 @@
       </c>
     </row>
     <row r="19" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D19" s="24"/>
+      <c r="D19" s="7"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
@@ -10476,7 +10210,7 @@
       </c>
     </row>
     <row r="20" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D20" s="24"/>
+      <c r="D20" s="7"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -10497,7 +10231,7 @@
       </c>
     </row>
     <row r="21" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D21" s="24"/>
+      <c r="D21" s="7"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
@@ -10518,7 +10252,7 @@
       </c>
     </row>
     <row r="22" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D22" s="24"/>
+      <c r="D22" s="7"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
@@ -10539,7 +10273,7 @@
       </c>
     </row>
     <row r="23" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D23" s="24"/>
+      <c r="D23" s="7"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
@@ -10560,7 +10294,7 @@
       </c>
     </row>
     <row r="24" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D24" s="24"/>
+      <c r="D24" s="7"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
@@ -10581,7 +10315,7 @@
       </c>
     </row>
     <row r="25" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D25" s="24"/>
+      <c r="D25" s="7"/>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
@@ -10602,7 +10336,7 @@
       </c>
     </row>
     <row r="26" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D26" s="24"/>
+      <c r="D26" s="7"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
@@ -10623,7 +10357,7 @@
       </c>
     </row>
     <row r="27" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D27" s="24"/>
+      <c r="D27" s="7"/>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
@@ -10644,7 +10378,7 @@
       </c>
     </row>
     <row r="28" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D28" s="24"/>
+      <c r="D28" s="7"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -10665,7 +10399,7 @@
       </c>
     </row>
     <row r="29" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D29" s="24"/>
+      <c r="D29" s="7"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -10686,7 +10420,7 @@
       </c>
     </row>
     <row r="30" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D30" s="24"/>
+      <c r="D30" s="7"/>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
@@ -10707,7 +10441,7 @@
       </c>
     </row>
     <row r="31" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D31" s="24"/>
+      <c r="D31" s="7"/>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
@@ -10728,7 +10462,7 @@
       </c>
     </row>
     <row r="32" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D32" s="24"/>
+      <c r="D32" s="7"/>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
@@ -10749,7 +10483,7 @@
       </c>
     </row>
     <row r="33" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D33" s="24"/>
+      <c r="D33" s="7"/>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
@@ -10770,7 +10504,7 @@
       </c>
     </row>
     <row r="34" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D34" s="24"/>
+      <c r="D34" s="7"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
@@ -10791,7 +10525,7 @@
       </c>
     </row>
     <row r="35" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D35" s="24"/>
+      <c r="D35" s="7"/>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
@@ -10812,7 +10546,7 @@
       </c>
     </row>
     <row r="36" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D36" s="24"/>
+      <c r="D36" s="7"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
@@ -10833,7 +10567,7 @@
       </c>
     </row>
     <row r="37" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D37" s="24"/>
+      <c r="D37" s="7"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
@@ -10854,7 +10588,7 @@
       </c>
     </row>
     <row r="38" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D38" s="24"/>
+      <c r="D38" s="7"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -10875,7 +10609,7 @@
       </c>
     </row>
     <row r="39" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D39" s="24"/>
+      <c r="D39" s="7"/>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
@@ -10896,7 +10630,7 @@
       </c>
     </row>
     <row r="40" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D40" s="24"/>
+      <c r="D40" s="7"/>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
@@ -10917,7 +10651,7 @@
       </c>
     </row>
     <row r="41" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D41" s="24"/>
+      <c r="D41" s="7"/>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
@@ -10938,7 +10672,7 @@
       </c>
     </row>
     <row r="42" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D42" s="24" t="s">
+      <c r="D42" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E42" s="5">
@@ -10972,22 +10706,22 @@
     <mergeCell ref="R1:R2"/>
     <mergeCell ref="S1:S2"/>
   </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>$M$3=$N$3</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="S3">
-    <cfRule type="expression" dxfId="65" priority="7">
+    <cfRule type="expression" dxfId="1" priority="7">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2">
-    <cfRule type="expression" dxfId="64" priority="8">
+    <cfRule type="expression" dxfId="0" priority="8">
       <formula>$AA$2="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="37" priority="1">
-      <formula>$AA$2="+"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="36" priority="2">
-      <formula>$M$3=$N$3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel/Profitus Rima.xlsx
+++ b/excel/Profitus Rima.xlsx
@@ -1,29 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Investavimas 2026.06.03\Profitus\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\Profitus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5114DB5D-8F19-4CA2-8665-6B9FC1EE7D73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02549EDE-7DFA-4C20-8BFF-65DD21C0B8A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="Pinigai" sheetId="12" r:id="rId2"/>
-    <sheet name="Druskonio Perlai, Druskininkai " sheetId="23" r:id="rId3"/>
-    <sheet name="Daugiabutis Druskininkuose V" sheetId="22" r:id="rId4"/>
-    <sheet name="Butas Didlaukio g., Vilnius II" sheetId="21" r:id="rId5"/>
-    <sheet name="Butai centrinėje Vilniaus dal." sheetId="20" r:id="rId6"/>
-    <sheet name="Sakurų Namai, Marijampolė III" sheetId="19" r:id="rId7"/>
-    <sheet name="Senvagės loftai, Panevėžys IV" sheetId="18" r:id="rId8"/>
+    <sheet name="Dvibutis prie Neries, Vilniaus " sheetId="25" r:id="rId3"/>
+    <sheet name="Huberto Namai, Trakų r. VII" sheetId="24" r:id="rId4"/>
+    <sheet name="Druskonio Perlai, Druskininkai " sheetId="23" r:id="rId5"/>
+    <sheet name="Daugiabutis Druskininkuose V" sheetId="22" r:id="rId6"/>
+    <sheet name="Butas Didlaukio g., Vilnius II" sheetId="21" r:id="rId7"/>
+    <sheet name="Butai centrinėje Vilniaus dal." sheetId="20" r:id="rId8"/>
+    <sheet name="Sakurų Namai, Marijampolė III" sheetId="19" r:id="rId9"/>
+    <sheet name="Senvagės loftai, Panevėžys IV" sheetId="18" r:id="rId10"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId11"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="67">
   <si>
     <t>Paskola</t>
   </si>
@@ -236,6 +238,18 @@
   <si>
     <t>Realus</t>
   </si>
+  <si>
+    <t>Huberto Namai, Trakų r. VII</t>
+  </si>
+  <si>
+    <t>Paskola P00001583-7</t>
+  </si>
+  <si>
+    <t>Paskola P00001642-2</t>
+  </si>
+  <si>
+    <t>Dvibutis prie Neries, Vilniaus r. II</t>
+  </si>
 </sst>
 </file>
 
@@ -280,18 +294,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="7">
@@ -385,7 +393,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -433,9 +441,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -447,6 +452,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -474,7 +488,77 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="31">
+  <dxfs count="41">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -726,7 +810,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9720A1A1-654C-48D3-A2F5-256753341D2A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36145E81-1DB2-4100-AAB4-F8645CD1142D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -782,7 +866,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AF1099C-6135-469F-AFC2-FF925627128E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{805339B6-7706-4601-A050-2D69C649EA21}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -838,7 +922,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{697C5CD6-B3D9-4668-8AE1-79DFCBDFA457}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9720A1A1-654C-48D3-A2F5-256753341D2A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -894,7 +978,7 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A364CBD-BB16-407C-BF42-C9E91FF5B88C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AF1099C-6135-469F-AFC2-FF925627128E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -950,6 +1034,118 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{697C5CD6-B3D9-4668-8AE1-79DFCBDFA457}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A364CBD-BB16-407C-BF42-C9E91FF5B88C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97A99DC0-5F06-4332-89FF-1020CAE6C409}"/>
             </a:ext>
           </a:extLst>
@@ -985,7 +1181,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1050,6 +1246,7 @@
     <sheetNames>
       <sheetName val="Overview"/>
       <sheetName val="Pinigai"/>
+      <sheetName val="Senvagės loftai, Panevėžys VIII"/>
       <sheetName val="Dvibučių kvartalas Kauno r. II"/>
       <sheetName val="Molėtų Oazė XII"/>
       <sheetName val="Europos 70, Kaunas XX"/>
@@ -1074,21 +1271,15 @@
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
-      <sheetData sheetId="3">
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4">
         <row r="2">
           <cell r="AA2" t="str">
             <v/>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5">
-        <row r="2">
-          <cell r="AA2" t="str">
-            <v/>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="5"/>
       <sheetData sheetId="6">
         <row r="2">
           <cell r="AA2" t="str">
@@ -1106,7 +1297,7 @@
       <sheetData sheetId="8">
         <row r="2">
           <cell r="AA2" t="str">
-            <v/>
+            <v>+</v>
           </cell>
         </row>
       </sheetData>
@@ -1145,13 +1336,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="14">
-        <row r="2">
-          <cell r="AA2" t="str">
-            <v/>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="14"/>
       <sheetData sheetId="15">
         <row r="2">
           <cell r="AA2" t="str">
@@ -1173,9 +1358,16 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="18"/>
+      <sheetData sheetId="18">
+        <row r="2">
+          <cell r="AA2" t="str">
+            <v/>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="19"/>
       <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1459,108 +1651,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="27" t="s">
+      <c r="A1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="O1" s="27" t="s">
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="O1" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27" t="s">
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="T1" s="27"/>
-      <c r="U1" s="28" t="s">
+      <c r="T1" s="29"/>
+      <c r="U1" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
+      <c r="V1" s="30"/>
+      <c r="W1" s="30"/>
+      <c r="X1" s="30"/>
     </row>
     <row r="2" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="I2" s="22" t="s">
+      <c r="I2" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="J2" s="22" t="s">
+      <c r="J2" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="K2" s="22" t="s">
+      <c r="K2" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="M2" s="23" t="s">
+      <c r="L2" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="M2" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="O2" s="23" t="s">
+      <c r="O2" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="P2" s="23" t="s">
+      <c r="P2" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="Q2" s="23" t="s">
+      <c r="Q2" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="23" t="s">
+      <c r="R2" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="S2" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="T2" s="23" t="s">
+      <c r="S2" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="T2" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="U2" s="23" t="s">
+      <c r="U2" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="V2" s="23" t="s">
+      <c r="V2" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="W2" s="23" t="s">
+      <c r="W2" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="X2" s="23" t="s">
+      <c r="X2" s="22" t="s">
         <v>37</v>
       </c>
       <c r="AC2" s="7" t="s">
@@ -1595,17 +1787,17 @@
         <f>'Senvagės loftai, Panevėžys IV'!B11</f>
         <v>100</v>
       </c>
-      <c r="H3" s="15">
+      <c r="H3" s="10">
         <f>'Senvagės loftai, Panevėžys IV'!B12</f>
         <v>46264</v>
       </c>
-      <c r="I3" s="15" t="str">
+      <c r="I3" s="10">
         <f>'Senvagės loftai, Panevėžys IV'!R3</f>
-        <v/>
-      </c>
-      <c r="J3" s="9">
+        <v>46248</v>
+      </c>
+      <c r="J3" s="9" t="str">
         <f ca="1">'Senvagės loftai, Panevėžys IV'!B13</f>
-        <v>27</v>
+        <v/>
       </c>
       <c r="K3" s="9" t="str">
         <f ca="1">'Senvagės loftai, Panevėžys IV'!S3</f>
@@ -1613,19 +1805,19 @@
       </c>
       <c r="L3" s="5">
         <f>'Senvagės loftai, Panevėžys IV'!N3</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M3" s="5">
         <f>'Senvagės loftai, Panevėžys IV'!P3</f>
-        <v>7.4500000000000011</v>
+        <v>8.56</v>
       </c>
       <c r="O3" s="5">
         <f>Pinigai!I2</f>
-        <v>624.35</v>
+        <v>623.95000000000005</v>
       </c>
       <c r="P3" s="5">
         <f>SUM(G3:G200)-S3</f>
-        <v>560.1</v>
+        <v>666.80000000000007</v>
       </c>
       <c r="Q3" s="5">
         <f>Pinigai!H2</f>
@@ -1633,31 +1825,31 @@
       </c>
       <c r="R3" s="5">
         <f>U3-P3</f>
-        <v>106.02999999999997</v>
+        <v>2.9099999999999682</v>
       </c>
       <c r="S3" s="5">
         <f>SUM(L3:L200)</f>
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T3" s="5">
         <f>SUM(M3:M200)</f>
-        <v>16.78</v>
+        <v>20.76</v>
       </c>
       <c r="U3" s="5">
         <f>O3+T3+Q3</f>
-        <v>666.13</v>
+        <v>669.71</v>
       </c>
       <c r="V3" s="5">
         <f>U3-O3</f>
-        <v>41.779999999999973</v>
+        <v>45.759999999999991</v>
       </c>
       <c r="W3" s="14">
         <f>(U3-O3)/O3</f>
-        <v>6.6917594298069941E-2</v>
+        <v>7.3339209872585923E-2</v>
       </c>
       <c r="X3" s="14">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.13586096167564396</v>
+        <v>0.12797755599021912</v>
       </c>
       <c r="AC3" s="9" t="str">
         <f ca="1">'Senvagės loftai, Panevėžys IV'!AA2</f>
@@ -1692,11 +1884,11 @@
         <f>'Sakurų Namai, Marijampolė III'!B11</f>
         <v>100</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="10">
         <f>'Sakurų Namai, Marijampolė III'!B12</f>
         <v>46265</v>
       </c>
-      <c r="I4" s="15">
+      <c r="I4" s="10">
         <f>'Sakurų Namai, Marijampolė III'!R3</f>
         <v>46154</v>
       </c>
@@ -1749,21 +1941,21 @@
         <f>'Butai centrinėje Vilniaus dal.'!B11</f>
         <v>125</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="10">
         <f>'Butai centrinėje Vilniaus dal.'!B12</f>
         <v>46258</v>
       </c>
-      <c r="I5" s="15" t="str">
+      <c r="I5" s="10" t="str">
         <f>'Butai centrinėje Vilniaus dal.'!R3</f>
         <v/>
       </c>
       <c r="J5" s="9">
         <f ca="1">'Butai centrinėje Vilniaus dal.'!B13</f>
-        <v>21</v>
+        <v>-8</v>
       </c>
       <c r="K5" s="9">
         <f ca="1">'Butai centrinėje Vilniaus dal.'!S3</f>
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="L5" s="5">
         <f>'Butai centrinėje Vilniaus dal.'!N3</f>
@@ -1806,17 +1998,17 @@
         <f>'Butas Didlaukio g., Vilnius II'!B11</f>
         <v>126.1</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="10">
         <f>'Butas Didlaukio g., Vilnius II'!B12</f>
         <v>46524</v>
       </c>
-      <c r="I6" s="15" t="str">
+      <c r="I6" s="10" t="str">
         <f>'Butas Didlaukio g., Vilnius II'!R3</f>
         <v/>
       </c>
       <c r="J6" s="9">
         <f ca="1">'Butas Didlaukio g., Vilnius II'!B13</f>
-        <v>287</v>
+        <v>258</v>
       </c>
       <c r="K6" s="9" t="str">
         <f ca="1">'Butas Didlaukio g., Vilnius II'!S3</f>
@@ -1828,7 +2020,7 @@
       </c>
       <c r="M6" s="5">
         <f>'Butas Didlaukio g., Vilnius II'!P3</f>
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC6" s="9" t="str">
         <f>'[1]Elfa loftai II'!AA2</f>
@@ -1863,21 +2055,21 @@
         <f>'Daugiabutis Druskininkuose V'!B11</f>
         <v>100</v>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="10">
         <f>'Daugiabutis Druskininkuose V'!B12</f>
         <v>46505</v>
       </c>
-      <c r="I7" s="15" t="str">
+      <c r="I7" s="10" t="str">
         <f>'Daugiabutis Druskininkuose V'!R3</f>
         <v/>
       </c>
       <c r="J7" s="9">
         <f ca="1">'Daugiabutis Druskininkuose V'!B13</f>
-        <v>268</v>
-      </c>
-      <c r="K7" s="9" t="str">
+        <v>239</v>
+      </c>
+      <c r="K7" s="9">
         <f ca="1">'Daugiabutis Druskininkuose V'!S3</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="L7" s="5">
         <f>'Daugiabutis Druskininkuose V'!N3</f>
@@ -1888,8 +2080,8 @@
         <v>0</v>
       </c>
       <c r="AC7" s="9" t="str">
-        <f>'[1]Kęstučio salos'!AA2</f>
-        <v/>
+        <f ca="1">'Daugiabutis Druskininkuose V'!AA2</f>
+        <v>+</v>
       </c>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.25">
@@ -1920,17 +2112,17 @@
         <f>'Druskonio Perlai, Druskininkai '!B11</f>
         <v>109</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="10">
         <f>'Druskonio Perlai, Druskininkai '!B12</f>
         <v>46559</v>
       </c>
-      <c r="I8" s="15" t="str">
+      <c r="I8" s="10" t="str">
         <f>'Druskonio Perlai, Druskininkai '!R3</f>
         <v/>
       </c>
       <c r="J8" s="9">
         <f ca="1">'Druskonio Perlai, Druskininkai '!B13</f>
-        <v>322</v>
+        <v>293</v>
       </c>
       <c r="K8" s="9" t="str">
         <f ca="1">'Druskonio Perlai, Druskininkai '!S3</f>
@@ -1944,8 +2136,8 @@
         <f>'Druskonio Perlai, Druskininkai '!P3</f>
         <v>0</v>
       </c>
-      <c r="AC8" s="9" t="str">
-        <f>'[1]Twinhouse XIII'!AA2</f>
+      <c r="AC8" s="5" t="str">
+        <f ca="1">'Druskonio Perlai, Druskininkai '!AA2</f>
         <v/>
       </c>
     </row>
@@ -1953,20 +2145,56 @@
       <c r="A9" s="3">
         <v>7</v>
       </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="AC9" s="9" t="str">
-        <f>'[1]Vyčio slėnis VIII'!AA2</f>
+      <c r="B9" s="10">
+        <f>'Huberto Namai, Trakų r. VII'!B3</f>
+        <v>46248</v>
+      </c>
+      <c r="C9" s="18" t="str">
+        <f>'Huberto Namai, Trakų r. VII'!B2</f>
+        <v>Huberto Namai, Trakų r. VII</v>
+      </c>
+      <c r="D9" s="3">
+        <f>'Huberto Namai, Trakų r. VII'!B8</f>
+        <v>12</v>
+      </c>
+      <c r="E9" s="3" t="str">
+        <f>'Huberto Namai, Trakų r. VII'!B5</f>
+        <v>A+</v>
+      </c>
+      <c r="F9" s="6">
+        <f>'Huberto Namai, Trakų r. VII'!B10</f>
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="G9" s="5">
+        <f>'Huberto Namai, Trakų r. VII'!B11</f>
+        <v>106.7</v>
+      </c>
+      <c r="H9" s="10">
+        <f>'Dvibutis prie Neries, Vilniaus '!B12</f>
+        <v>46615</v>
+      </c>
+      <c r="I9" s="10" t="str">
+        <f>'Huberto Namai, Trakų r. VII'!R3</f>
+        <v/>
+      </c>
+      <c r="J9" s="9">
+        <f ca="1">'Huberto Namai, Trakų r. VII'!B13</f>
+        <v>349</v>
+      </c>
+      <c r="K9" s="9" t="str">
+        <f ca="1">'Huberto Namai, Trakų r. VII'!S3</f>
+        <v/>
+      </c>
+      <c r="L9" s="5">
+        <f>'Huberto Namai, Trakų r. VII'!N3</f>
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <f>'Huberto Namai, Trakų r. VII'!P3</f>
+        <v>0</v>
+      </c>
+      <c r="AC9" s="5" t="str">
+        <f ca="1">'Huberto Namai, Trakų r. VII'!AA2</f>
         <v/>
       </c>
     </row>
@@ -1974,20 +2202,56 @@
       <c r="A10" s="3">
         <v>8</v>
       </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="AC10" s="9" t="str">
-        <f>'[1]Dvibutis Upės g.'!AA2</f>
+      <c r="B10" s="10">
+        <f>'Dvibutis prie Neries, Vilniaus '!B3</f>
+        <v>46248</v>
+      </c>
+      <c r="C10" s="18" t="str">
+        <f>'Dvibutis prie Neries, Vilniaus '!B2</f>
+        <v>Dvibutis prie Neries, Vilniaus r. II</v>
+      </c>
+      <c r="D10" s="3">
+        <f>'Dvibutis prie Neries, Vilniaus '!B8</f>
+        <v>12</v>
+      </c>
+      <c r="E10" s="3" t="str">
+        <f>'Dvibutis prie Neries, Vilniaus '!B5</f>
+        <v>A</v>
+      </c>
+      <c r="F10" s="6">
+        <f>'Dvibutis prie Neries, Vilniaus '!B10</f>
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="G10" s="5">
+        <f>'Dvibutis prie Neries, Vilniaus '!B11</f>
+        <v>100</v>
+      </c>
+      <c r="H10" s="10">
+        <f>'Dvibutis prie Neries, Vilniaus '!B12</f>
+        <v>46615</v>
+      </c>
+      <c r="I10" s="10" t="str">
+        <f>'Dvibutis prie Neries, Vilniaus '!R3</f>
+        <v/>
+      </c>
+      <c r="J10" s="9">
+        <f ca="1">'Dvibutis prie Neries, Vilniaus '!B13</f>
+        <v>349</v>
+      </c>
+      <c r="K10" s="9" t="str">
+        <f ca="1">'Dvibutis prie Neries, Vilniaus '!S3</f>
+        <v/>
+      </c>
+      <c r="L10" s="5">
+        <f>'Dvibutis prie Neries, Vilniaus '!N3</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <f>'Dvibutis prie Neries, Vilniaus '!P3</f>
+        <v>0</v>
+      </c>
+      <c r="AC10" s="5" t="str">
+        <f ca="1">'Dvibutis prie Neries, Vilniaus '!AA2</f>
         <v/>
       </c>
     </row>
@@ -2001,8 +2265,8 @@
       <c r="E11" s="3"/>
       <c r="F11" s="6"/>
       <c r="G11" s="5"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
       <c r="L11" s="5"/>
@@ -2022,8 +2286,8 @@
       <c r="E12" s="3"/>
       <c r="F12" s="6"/>
       <c r="G12" s="5"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
       <c r="J12" s="9"/>
       <c r="K12" s="9"/>
       <c r="L12" s="5"/>
@@ -2043,8 +2307,8 @@
       <c r="E13" s="3"/>
       <c r="F13" s="6"/>
       <c r="G13" s="5"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
       <c r="J13" s="9"/>
       <c r="K13" s="9"/>
       <c r="L13" s="5"/>
@@ -2064,8 +2328,8 @@
       <c r="E14" s="3"/>
       <c r="F14" s="6"/>
       <c r="G14" s="5"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
       <c r="J14" s="9"/>
       <c r="K14" s="9"/>
       <c r="L14" s="5"/>
@@ -2085,8 +2349,8 @@
       <c r="E15" s="3"/>
       <c r="F15" s="6"/>
       <c r="G15" s="5"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
       <c r="J15" s="9"/>
       <c r="K15" s="9"/>
       <c r="L15" s="5"/>
@@ -2106,16 +2370,13 @@
       <c r="E16" s="3"/>
       <c r="F16" s="6"/>
       <c r="G16" s="5"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
       <c r="J16" s="9"/>
       <c r="K16" s="9"/>
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
-      <c r="AC16" s="9" t="str">
-        <f>'[1]Golf Hills Vilos, Alikantė'!AA2</f>
-        <v/>
-      </c>
+      <c r="AC16" s="9"/>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
@@ -2127,8 +2388,8 @@
       <c r="E17" s="3"/>
       <c r="F17" s="6"/>
       <c r="G17" s="5"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
       <c r="J17" s="9"/>
       <c r="K17" s="9"/>
       <c r="L17" s="5"/>
@@ -2148,8 +2409,8 @@
       <c r="E18" s="3"/>
       <c r="F18" s="6"/>
       <c r="G18" s="5"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
       <c r="J18" s="9"/>
       <c r="K18" s="9"/>
       <c r="L18" s="5"/>
@@ -2169,8 +2430,8 @@
       <c r="E19" s="3"/>
       <c r="F19" s="6"/>
       <c r="G19" s="5"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
       <c r="L19" s="5"/>
@@ -2187,8 +2448,8 @@
       <c r="E20" s="3"/>
       <c r="F20" s="6"/>
       <c r="G20" s="5"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
       <c r="J20" s="9"/>
       <c r="K20" s="9"/>
       <c r="L20" s="5"/>
@@ -2208,8 +2469,8 @@
       <c r="E21" s="3"/>
       <c r="F21" s="6"/>
       <c r="G21" s="5"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
       <c r="L21" s="5"/>
@@ -2224,8 +2485,8 @@
       <c r="E22" s="3"/>
       <c r="F22" s="6"/>
       <c r="G22" s="5"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
       <c r="J22" s="9"/>
       <c r="K22" s="9"/>
       <c r="L22" s="5"/>
@@ -2240,8 +2501,8 @@
       <c r="E23" s="3"/>
       <c r="F23" s="6"/>
       <c r="G23" s="5"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
       <c r="J23" s="9"/>
       <c r="K23" s="9"/>
       <c r="L23" s="5"/>
@@ -2256,8 +2517,8 @@
       <c r="E24" s="3"/>
       <c r="F24" s="6"/>
       <c r="G24" s="5"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
       <c r="J24" s="9"/>
       <c r="K24" s="9"/>
       <c r="L24" s="5"/>
@@ -2272,8 +2533,8 @@
       <c r="E25" s="3"/>
       <c r="F25" s="6"/>
       <c r="G25" s="5"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
       <c r="L25" s="5"/>
@@ -2288,8 +2549,8 @@
       <c r="E26" s="3"/>
       <c r="F26" s="6"/>
       <c r="G26" s="5"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
       <c r="J26" s="9"/>
       <c r="K26" s="9"/>
       <c r="L26" s="5"/>
@@ -2304,8 +2565,8 @@
       <c r="E27" s="3"/>
       <c r="F27" s="6"/>
       <c r="G27" s="5"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
       <c r="J27" s="9"/>
       <c r="K27" s="9"/>
       <c r="L27" s="5"/>
@@ -2324,34 +2585,42 @@
     <mergeCell ref="U1:X1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:M27">
-    <cfRule type="expression" dxfId="30" priority="1">
+    <cfRule type="expression" dxfId="40" priority="3">
       <formula>$AC3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="2">
+    <cfRule type="expression" dxfId="39" priority="4">
       <formula>AND($G3&gt;0,$G3=$L3)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC4">
-    <cfRule type="expression" dxfId="28" priority="6">
+    <cfRule type="expression" dxfId="38" priority="8">
       <formula>$AC$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC4:AC5">
-    <cfRule type="expression" dxfId="27" priority="3">
+    <cfRule type="expression" dxfId="37" priority="5">
       <formula>AND($G4&gt;0,$G4=$L4)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC5">
-    <cfRule type="expression" dxfId="26" priority="4">
+    <cfRule type="expression" dxfId="36" priority="6">
       <formula>#REF!="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC20">
-    <cfRule type="expression" dxfId="25" priority="7">
+    <cfRule type="expression" dxfId="35" priority="9">
       <formula>AND($G20&gt;0,$G20=$L20)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="8">
+    <cfRule type="expression" dxfId="34" priority="10">
       <formula>$AC20="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC8:AC10">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$AC8="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>AND($G8&gt;0,$G8=$L8)</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -2361,9 +2630,1177 @@
     <hyperlink ref="C6" location="'Butas Didlaukio g., Vilnius II'!A1" display="'Butas Didlaukio g., Vilnius II'!A1" xr:uid="{36EDC278-83F2-48B4-BDA9-6C1FA86323D7}"/>
     <hyperlink ref="C7" location="'Daugiabutis Druskininkuose V'!A1" display="'Daugiabutis Druskininkuose V'!A1" xr:uid="{CB86F671-B0F6-4A77-A66E-BC2B01A2D347}"/>
     <hyperlink ref="C8" location="'Druskonio Perlai, Druskininkai '!A1" display="'Druskonio Perlai, Druskininkai '!A1" xr:uid="{086EB93A-D255-454D-8C6B-C6ECE41471B3}"/>
+    <hyperlink ref="C9" location="'Huberto Namai, Trakų r. VII'!A1" display="'Huberto Namai, Trakų r. VII'!A1" xr:uid="{D749133E-F7B6-4C11-9981-3A75EFAE65F0}"/>
+    <hyperlink ref="C10" location="'Dvibutis prie Neries, Vilniaus '!A1" display="'Dvibutis prie Neries, Vilniaus '!A1" xr:uid="{BA62E006-4493-4139-8B01-5343F20E4C1B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBBD8F82-98DB-47B3-A2A6-B135C5884EA9}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:AA42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="1" customWidth="1"/>
+    <col min="5" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" customWidth="1"/>
+    <col min="13" max="19" width="10.7109375" customWidth="1"/>
+    <col min="20" max="24" width="8.7109375" customWidth="1"/>
+    <col min="25" max="27" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="28"/>
+      <c r="O1" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="R1" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y1" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z1" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA1" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="10">
+        <v>46022</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5">
+        <v>2.99</v>
+      </c>
+      <c r="G2" s="5">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5">
+        <v>2.99</v>
+      </c>
+      <c r="I2" s="5">
+        <v>0</v>
+      </c>
+      <c r="J2" s="10">
+        <v>46022</v>
+      </c>
+      <c r="K2" s="9">
+        <f>IF(J2&gt;0,J2-D2,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M2" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="Y2" s="10">
+        <f>B3</f>
+        <v>45899</v>
+      </c>
+      <c r="Z2" s="3">
+        <f>B11*-1</f>
+        <v>-100</v>
+      </c>
+      <c r="AA2" s="3" t="str">
+        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="10">
+        <v>45899</v>
+      </c>
+      <c r="D3" s="10">
+        <v>46112</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="10">
+        <v>46112</v>
+      </c>
+      <c r="K3" s="9">
+        <f t="shared" ref="K3:K41" si="0">IF(J3&gt;0,J3-D3,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <f>B11</f>
+        <v>100</v>
+      </c>
+      <c r="N3" s="5">
+        <f>G42</f>
+        <v>100</v>
+      </c>
+      <c r="O3" s="5">
+        <f>F42</f>
+        <v>8.9600000000000009</v>
+      </c>
+      <c r="P3" s="5">
+        <f>H42+I42</f>
+        <v>8.56</v>
+      </c>
+      <c r="Q3" s="14">
+        <f>IF(M3=N3,XIRR(Z2:Z41,Y2:Y41),"")</f>
+        <v>9.2495992779731764E-2</v>
+      </c>
+      <c r="R3" s="10">
+        <f>IF(M3=N3,B14,"")</f>
+        <v>46248</v>
+      </c>
+      <c r="S3" s="3" t="str">
+        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
+        <v/>
+      </c>
+      <c r="Y3" s="10">
+        <f>J2</f>
+        <v>46022</v>
+      </c>
+      <c r="Z3" s="5">
+        <f>G2+H2+I2</f>
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="10">
+        <v>45901</v>
+      </c>
+      <c r="D4" s="10">
+        <v>46203</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="10">
+        <v>46204</v>
+      </c>
+      <c r="K4" s="9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Y4" s="10">
+        <f t="shared" ref="Y4:Y41" si="1">J3</f>
+        <v>46112</v>
+      </c>
+      <c r="Z4" s="5">
+        <f t="shared" ref="Z4:Z41" si="2">G3+H3+I3</f>
+        <v>2.2200000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="10">
+        <v>46264</v>
+      </c>
+      <c r="E5" s="5">
+        <v>100</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1.51</v>
+      </c>
+      <c r="G5" s="3">
+        <v>100</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="10">
+        <v>46248</v>
+      </c>
+      <c r="K5" s="9">
+        <f t="shared" si="0"/>
+        <v>-16</v>
+      </c>
+      <c r="Y5" s="10">
+        <f t="shared" si="1"/>
+        <v>46204</v>
+      </c>
+      <c r="Z5" s="5">
+        <f t="shared" si="2"/>
+        <v>2.2400000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.59</v>
+      </c>
+      <c r="D6" s="10"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y6" s="10">
+        <f t="shared" si="1"/>
+        <v>46248</v>
+      </c>
+      <c r="Z6" s="5">
+        <f t="shared" si="2"/>
+        <v>101.11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z7" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3">
+        <v>12</v>
+      </c>
+      <c r="D8" s="10"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y8" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z8" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z9" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="6">
+        <v>0.09</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="5">
+        <v>100</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z11" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="10">
+        <v>46264</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y12" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z12" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="9" t="str">
+        <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
+        <v/>
+      </c>
+      <c r="D13" s="10"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y13" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="10">
+        <v>46248</v>
+      </c>
+      <c r="D14" s="7"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y14" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z14" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="3">
+        <f>IF(M3=N3,B14-B12,"")</f>
+        <v>-16</v>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y15" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z15" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="D16" s="7"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y16" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D17" s="7"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y17" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z17" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D18" s="7"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y18" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z18" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D19" s="7"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y19" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z19" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D20" s="7"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y20" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z20" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D21" s="7"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y21" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z21" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D22" s="7"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y22" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z22" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D23" s="7"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y23" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z23" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D24" s="7"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y24" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z24" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D25" s="7"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y25" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z25" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D26" s="7"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y26" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z26" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D27" s="7"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y27" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z27" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D28" s="7"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y28" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z28" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D29" s="7"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y29" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z29" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D30" s="7"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y30" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z30" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D31" s="7"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y31" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z31" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D32" s="7"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y32" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z32" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D33" s="7"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y33" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z33" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D34" s="7"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y34" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z34" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D35" s="7"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y35" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z35" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D36" s="7"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y36" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z36" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D37" s="7"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y37" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z37" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D38" s="7"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y38" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z38" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D39" s="7"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y39" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z39" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D40" s="7"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y40" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z40" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D41" s="7"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y41" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z41" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D42" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="5">
+        <f>SUM(E2:E41)</f>
+        <v>100</v>
+      </c>
+      <c r="F42" s="5">
+        <f t="shared" ref="F42:I42" si="3">SUM(F2:F41)</f>
+        <v>8.9600000000000009</v>
+      </c>
+      <c r="G42" s="5">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="H42" s="5">
+        <f t="shared" si="3"/>
+        <v>8.56</v>
+      </c>
+      <c r="I42" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="R1:R2"/>
+    <mergeCell ref="S1:S2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>$M$3=$N$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S3">
+    <cfRule type="expression" dxfId="3" priority="7">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2">
+    <cfRule type="expression" dxfId="2" priority="8">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2372,7 +3809,7 @@
   <dimension ref="A1:L200"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" style="20" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" style="19" customWidth="1"/>
     <col min="2" max="4" width="10.7109375" customWidth="1"/>
     <col min="5" max="5" width="8.7109375" customWidth="1"/>
     <col min="6" max="9" width="10.7109375" customWidth="1"/>
@@ -2408,9 +3845,9 @@
       <c r="K1" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="21">
+      <c r="L1" s="20">
         <f ca="1">XIRR(K2:K200,A2:A200)</f>
-        <v>0.13586096167564396</v>
+        <v>0.12797755599021912</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -2428,7 +3865,7 @@
       </c>
       <c r="F2" s="5">
         <f>SUM(B2:B36)</f>
-        <v>624.35</v>
+        <v>623.95000000000005</v>
       </c>
       <c r="G2" s="5">
         <f>SUM(C2:C36)</f>
@@ -2440,7 +3877,7 @@
       </c>
       <c r="I2" s="5">
         <f>F2-G2</f>
-        <v>624.35</v>
+        <v>623.95000000000005</v>
       </c>
       <c r="K2" s="5">
         <f>B2*-1</f>
@@ -2487,8 +3924,8 @@
       <c r="A5" s="10">
         <v>46171</v>
       </c>
-      <c r="B5" s="19">
-        <v>108.96</v>
+      <c r="B5" s="24">
+        <v>108.56</v>
       </c>
       <c r="C5" s="5">
         <v>0</v>
@@ -2498,7 +3935,7 @@
       </c>
       <c r="K5" s="5">
         <f t="shared" si="0"/>
-        <v>-108.96</v>
+        <v>-108.56</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -3876,14 +5313,14 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="10">
         <f ca="1">TODAY()</f>
-        <v>46237</v>
+        <v>46266</v>
       </c>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
       <c r="K200" s="5">
         <f>Overview!U3</f>
-        <v>666.13</v>
+        <v>669.71</v>
       </c>
     </row>
   </sheetData>
@@ -3893,6 +5330,2264 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72C83585-76E8-43FA-B139-66F5B08DA1B3}">
+  <dimension ref="A1:AA42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="1" customWidth="1"/>
+    <col min="5" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" customWidth="1"/>
+    <col min="13" max="19" width="10.7109375" customWidth="1"/>
+    <col min="20" max="24" width="8.7109375" customWidth="1"/>
+    <col min="25" max="27" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="28"/>
+      <c r="O1" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="R1" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y1" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z1" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA1" s="23" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="10">
+        <v>46363</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5">
+        <v>2.48</v>
+      </c>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="9" t="str">
+        <f>IF(J2&gt;0,J2-D2,"")</f>
+        <v/>
+      </c>
+      <c r="M2" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="P2" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="Y2" s="10">
+        <f>B3</f>
+        <v>46248</v>
+      </c>
+      <c r="Z2" s="3">
+        <f>B11*-1</f>
+        <v>-100</v>
+      </c>
+      <c r="AA2" s="3" t="str">
+        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="10">
+        <v>46248</v>
+      </c>
+      <c r="D3" s="10">
+        <v>46453</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>2.15</v>
+      </c>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="9" t="str">
+        <f t="shared" ref="K3:K41" si="0">IF(J3&gt;0,J3-D3,"")</f>
+        <v/>
+      </c>
+      <c r="M3" s="5">
+        <f>B11</f>
+        <v>100</v>
+      </c>
+      <c r="N3" s="5">
+        <f>G42</f>
+        <v>0</v>
+      </c>
+      <c r="O3" s="5">
+        <f>F42</f>
+        <v>8.66</v>
+      </c>
+      <c r="P3" s="5">
+        <f>H42+I42</f>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="14" t="str">
+        <f>IF(M3=N3,XIRR(Z2:Z41,Y2:Y41),"")</f>
+        <v/>
+      </c>
+      <c r="R3" s="10" t="str">
+        <f>IF(M3=N3,B14,"")</f>
+        <v/>
+      </c>
+      <c r="S3" s="3" t="str">
+        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
+        <v/>
+      </c>
+      <c r="Y3" s="10">
+        <f>J2</f>
+        <v>0</v>
+      </c>
+      <c r="Z3" s="5">
+        <f>G2+H2+I2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="10">
+        <v>46252</v>
+      </c>
+      <c r="D4" s="10">
+        <v>46545</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>2.19</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y4" s="10">
+        <f t="shared" ref="Y4:Y41" si="1">J3</f>
+        <v>0</v>
+      </c>
+      <c r="Z4" s="5">
+        <f t="shared" ref="Z4:Z41" si="2">G3+H3+I3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="10">
+        <v>46615</v>
+      </c>
+      <c r="E5" s="5">
+        <v>100</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1.84</v>
+      </c>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y5" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z5" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="D6" s="10"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y6" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z7" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3">
+        <v>12</v>
+      </c>
+      <c r="D8" s="10"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y8" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z8" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z9" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="6">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="5">
+        <v>100</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z11" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="25">
+        <v>46615</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y12" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z12" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="9">
+        <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
+        <v>349</v>
+      </c>
+      <c r="D13" s="10"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y13" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y14" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z14" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="3" t="str">
+        <f>IF(M3=N3,B14-B12,"")</f>
+        <v/>
+      </c>
+      <c r="D15" s="23"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y15" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z15" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="D16" s="23"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y16" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D17" s="23"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y17" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z17" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D18" s="23"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y18" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z18" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D19" s="23"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y19" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z19" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D20" s="23"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y20" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z20" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D21" s="23"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y21" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z21" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D22" s="23"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y22" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z22" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D23" s="23"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y23" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z23" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D24" s="23"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y24" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z24" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D25" s="23"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y25" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z25" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D26" s="23"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y26" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z26" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D27" s="23"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y27" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z27" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D28" s="23"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y28" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z28" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D29" s="23"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y29" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z29" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D30" s="23"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y30" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z30" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D31" s="23"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y31" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z31" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D32" s="23"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y32" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z32" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D33" s="23"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y33" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z33" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D34" s="23"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y34" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z34" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D35" s="23"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y35" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z35" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D36" s="23"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y36" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z36" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D37" s="23"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y37" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z37" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D38" s="23"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y38" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z38" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D39" s="23"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y39" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z39" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D40" s="23"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y40" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z40" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D41" s="23"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y41" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z41" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D42" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="5">
+        <f>SUM(E2:E41)</f>
+        <v>100</v>
+      </c>
+      <c r="F42" s="5">
+        <f t="shared" ref="F42:I42" si="3">SUM(F2:F41)</f>
+        <v>8.66</v>
+      </c>
+      <c r="G42" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I42" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="R1:R2"/>
+    <mergeCell ref="S1:S2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="33" priority="1">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="2">
+      <formula>$M$3=$N$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S3">
+    <cfRule type="expression" dxfId="31" priority="3">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2">
+    <cfRule type="expression" dxfId="30" priority="4">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDB1F80C-A6D2-499E-B2A1-FB3EEC0E6D72}">
+  <dimension ref="A1:AA42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="1" customWidth="1"/>
+    <col min="5" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" customWidth="1"/>
+    <col min="13" max="19" width="10.7109375" customWidth="1"/>
+    <col min="20" max="24" width="8.7109375" customWidth="1"/>
+    <col min="25" max="27" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="28"/>
+      <c r="O1" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="R1" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y1" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z1" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA1" s="23" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="10">
+        <v>46363</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="9" t="str">
+        <f>IF(J2&gt;0,J2-D2,"")</f>
+        <v/>
+      </c>
+      <c r="M2" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="P2" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="Y2" s="10">
+        <f>B3</f>
+        <v>46248</v>
+      </c>
+      <c r="Z2" s="3">
+        <f>B11*-1</f>
+        <v>-106.7</v>
+      </c>
+      <c r="AA2" s="3" t="str">
+        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="10">
+        <v>46248</v>
+      </c>
+      <c r="D3" s="10">
+        <v>46453</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>2.21</v>
+      </c>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="9" t="str">
+        <f t="shared" ref="K3:K41" si="0">IF(J3&gt;0,J3-D3,"")</f>
+        <v/>
+      </c>
+      <c r="M3" s="5">
+        <f>B11</f>
+        <v>106.7</v>
+      </c>
+      <c r="N3" s="5">
+        <f>G42</f>
+        <v>0</v>
+      </c>
+      <c r="O3" s="5">
+        <f>F42</f>
+        <v>8.91</v>
+      </c>
+      <c r="P3" s="5">
+        <f>H42+I42</f>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="14" t="str">
+        <f>IF(M3=N3,XIRR(Z2:Z41,Y2:Y41),"")</f>
+        <v/>
+      </c>
+      <c r="R3" s="10" t="str">
+        <f>IF(M3=N3,B14,"")</f>
+        <v/>
+      </c>
+      <c r="S3" s="3" t="str">
+        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
+        <v/>
+      </c>
+      <c r="Y3" s="10">
+        <f>J2</f>
+        <v>0</v>
+      </c>
+      <c r="Z3" s="5">
+        <f>G2+H2+I2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="10">
+        <v>46252</v>
+      </c>
+      <c r="D4" s="10">
+        <v>46545</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y4" s="10">
+        <f t="shared" ref="Y4:Y41" si="1">J3</f>
+        <v>0</v>
+      </c>
+      <c r="Z4" s="5">
+        <f t="shared" ref="Z4:Z41" si="2">G3+H3+I3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="10">
+        <v>46615</v>
+      </c>
+      <c r="E5" s="5">
+        <v>106.7</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1.89</v>
+      </c>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y5" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z5" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.61</v>
+      </c>
+      <c r="D6" s="10"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y6" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.85</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y7" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z7" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3">
+        <v>12</v>
+      </c>
+      <c r="D8" s="10"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y8" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z8" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y9" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z9" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="6">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y10" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="5">
+        <v>106.7</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z11" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="25">
+        <v>46615</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y12" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z12" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="9">
+        <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
+        <v>349</v>
+      </c>
+      <c r="D13" s="10"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y13" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y14" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z14" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="3" t="str">
+        <f>IF(M3=N3,B14-B12,"")</f>
+        <v/>
+      </c>
+      <c r="D15" s="23"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y15" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z15" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="D16" s="23"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y16" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D17" s="23"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y17" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z17" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D18" s="23"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y18" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z18" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D19" s="23"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y19" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z19" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D20" s="23"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y20" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z20" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D21" s="23"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y21" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z21" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D22" s="23"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y22" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z22" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D23" s="23"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y23" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z23" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D24" s="23"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y24" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z24" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D25" s="23"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y25" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z25" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D26" s="23"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y26" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z26" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D27" s="23"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y27" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z27" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D28" s="23"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y28" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z28" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D29" s="23"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y29" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z29" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D30" s="23"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y30" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z30" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D31" s="23"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y31" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z31" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D32" s="23"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y32" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z32" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D33" s="23"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y33" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z33" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D34" s="23"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y34" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z34" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D35" s="23"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y35" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z35" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D36" s="23"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y36" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z36" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D37" s="23"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y37" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z37" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D38" s="23"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y38" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z38" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D39" s="23"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y39" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z39" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D40" s="23"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y40" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z40" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D41" s="23"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y41" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z41" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D42" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="5">
+        <f>SUM(E2:E41)</f>
+        <v>106.7</v>
+      </c>
+      <c r="F42" s="5">
+        <f t="shared" ref="F42:I42" si="3">SUM(F2:F41)</f>
+        <v>8.91</v>
+      </c>
+      <c r="G42" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I42" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="R1:R2"/>
+    <mergeCell ref="S1:S2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="29" priority="1">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="2">
+      <formula>$M$3=$N$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S3">
+    <cfRule type="expression" dxfId="27" priority="3">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2">
+    <cfRule type="expression" dxfId="26" priority="4">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D346BFD8-B0E5-40D5-BEAF-A5929613C1CA}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3941,21 +7636,21 @@
       <c r="K1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="26"/>
-      <c r="O1" s="24" t="s">
+      <c r="M1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="28"/>
+      <c r="O1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="29" t="s">
+      <c r="P1" s="28"/>
+      <c r="Q1" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="R1" s="29" t="s">
+      <c r="R1" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="29" t="s">
+      <c r="S1" s="31" t="s">
         <v>47</v>
       </c>
       <c r="Y1" s="12" t="s">
@@ -4004,9 +7699,9 @@
       <c r="P2" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
       <c r="Y2" s="10">
         <f>B3</f>
         <v>46191</v>
@@ -4342,7 +8037,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>322</v>
+        <v>293</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="5"/>
@@ -4999,20 +8694,20 @@
     <mergeCell ref="S1:S2"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>$AA$2="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="2">
+    <cfRule type="expression" dxfId="24" priority="2">
       <formula>$M$3=$N$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S3">
-    <cfRule type="expression" dxfId="21" priority="7">
+    <cfRule type="expression" dxfId="23" priority="7">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2">
-    <cfRule type="expression" dxfId="20" priority="8">
+    <cfRule type="expression" dxfId="22" priority="8">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5021,7 +8716,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{810D7EBF-D756-4489-B8DD-C1D562CD5B73}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5070,21 +8765,21 @@
       <c r="K1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="26"/>
-      <c r="O1" s="24" t="s">
+      <c r="M1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="28"/>
+      <c r="O1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="29" t="s">
+      <c r="P1" s="28"/>
+      <c r="Q1" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="R1" s="29" t="s">
+      <c r="R1" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="29" t="s">
+      <c r="S1" s="31" t="s">
         <v>47</v>
       </c>
       <c r="Y1" s="12" t="s">
@@ -5133,9 +8828,9 @@
       <c r="P2" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
       <c r="Y2" s="10">
         <f>B3</f>
         <v>46161</v>
@@ -5146,7 +8841,7 @@
       </c>
       <c r="AA2" s="3" t="str">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
-        <v/>
+        <v>+</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -5197,9 +8892,9 @@
         <f>IF(M3=N3,B14,"")</f>
         <v/>
       </c>
-      <c r="S3" s="3" t="str">
+      <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y3" s="10">
         <f>J2</f>
@@ -5471,7 +9166,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>268</v>
+        <v>239</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="5"/>
@@ -6128,20 +9823,20 @@
     <mergeCell ref="S1:S2"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>$AA$2="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="2">
+    <cfRule type="expression" dxfId="20" priority="2">
       <formula>$M$3=$N$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S3">
-    <cfRule type="expression" dxfId="17" priority="7">
+    <cfRule type="expression" dxfId="19" priority="7">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2">
-    <cfRule type="expression" dxfId="16" priority="8">
+    <cfRule type="expression" dxfId="18" priority="8">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6150,7 +9845,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74623EE0-3021-4A72-B22C-29C64B41A950}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6199,21 +9894,21 @@
       <c r="K1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="26"/>
-      <c r="O1" s="24" t="s">
+      <c r="M1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="28"/>
+      <c r="O1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="29" t="s">
+      <c r="P1" s="28"/>
+      <c r="Q1" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="R1" s="29" t="s">
+      <c r="R1" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="29" t="s">
+      <c r="S1" s="31" t="s">
         <v>47</v>
       </c>
       <c r="Y1" s="12" t="s">
@@ -6242,13 +9937,21 @@
       <c r="F2" s="5">
         <v>2.87</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="9" t="str">
+      <c r="G2" s="5">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5">
+        <v>2.87</v>
+      </c>
+      <c r="I2" s="5">
+        <v>0</v>
+      </c>
+      <c r="J2" s="10">
+        <v>46266</v>
+      </c>
+      <c r="K2" s="9">
         <f>IF(J2&gt;0,J2-D2,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M2" s="13" t="s">
         <v>39</v>
@@ -6262,9 +9965,9 @@
       <c r="P2" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
       <c r="Y2" s="10">
         <f>B3</f>
         <v>46157</v>
@@ -6316,7 +10019,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q3" s="14" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z41,Y2:Y41),"")</f>
@@ -6332,11 +10035,11 @@
       </c>
       <c r="Y3" s="10">
         <f>J2</f>
-        <v>0</v>
+        <v>46266</v>
       </c>
       <c r="Z3" s="5">
         <f>G2+H2+I2</f>
-        <v>0</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
@@ -6600,7 +10303,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>287</v>
+        <v>258</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="5"/>
@@ -7239,7 +10942,7 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="3"/>
@@ -7257,20 +10960,20 @@
     <mergeCell ref="S1:S2"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>$AA$2="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="2">
+    <cfRule type="expression" dxfId="16" priority="2">
       <formula>$M$3=$N$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S3">
-    <cfRule type="expression" dxfId="13" priority="11">
+    <cfRule type="expression" dxfId="15" priority="11">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2">
-    <cfRule type="expression" dxfId="12" priority="12">
+    <cfRule type="expression" dxfId="14" priority="12">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7279,8 +10982,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1447860C-6895-4117-8CA4-0B2D4DA1EC46}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7328,21 +11034,21 @@
       <c r="K1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="26"/>
-      <c r="O1" s="24" t="s">
+      <c r="M1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="28"/>
+      <c r="O1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="29" t="s">
+      <c r="P1" s="28"/>
+      <c r="Q1" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="R1" s="29" t="s">
+      <c r="R1" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="29" t="s">
+      <c r="S1" s="31" t="s">
         <v>47</v>
       </c>
       <c r="Y1" s="12" t="s">
@@ -7399,9 +11105,9 @@
       <c r="P2" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
       <c r="Y2" s="10">
         <f>B3</f>
         <v>45979</v>
@@ -7465,7 +11171,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="Y3" s="10">
         <f>J2</f>
@@ -7731,7 +11437,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>21</v>
+        <v>-8</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="5"/>
@@ -8388,20 +12094,20 @@
     <mergeCell ref="S1:S2"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>$AA$2="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="2">
+    <cfRule type="expression" dxfId="12" priority="2">
       <formula>$M$3=$N$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S3">
-    <cfRule type="expression" dxfId="9" priority="11">
+    <cfRule type="expression" dxfId="11" priority="11">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2">
-    <cfRule type="expression" dxfId="8" priority="12">
+    <cfRule type="expression" dxfId="10" priority="12">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8410,7 +12116,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6415147-B736-4A0C-95EF-0F86A2EF4544}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -8462,21 +12168,21 @@
       <c r="K1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="26"/>
-      <c r="O1" s="24" t="s">
+      <c r="M1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="28"/>
+      <c r="O1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="29" t="s">
+      <c r="P1" s="28"/>
+      <c r="Q1" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="R1" s="29" t="s">
+      <c r="R1" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="29" t="s">
+      <c r="S1" s="31" t="s">
         <v>47</v>
       </c>
       <c r="Y1" s="12" t="s">
@@ -8533,9 +12239,9 @@
       <c r="P2" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
       <c r="Y2" s="10">
         <f>B3</f>
         <v>45899</v>
@@ -9554,1173 +13260,20 @@
     <mergeCell ref="S1:S2"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>$AA$2="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="8" priority="2">
       <formula>$M$3=$N$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S3">
-    <cfRule type="expression" dxfId="5" priority="9">
+    <cfRule type="expression" dxfId="7" priority="9">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2">
-    <cfRule type="expression" dxfId="4" priority="10">
-      <formula>$AA$2="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBBD8F82-98DB-47B3-A2A6-B135C5884EA9}">
-  <dimension ref="A1:AA42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="1" customWidth="1"/>
-    <col min="5" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="8.7109375" customWidth="1"/>
-    <col min="13" max="19" width="10.7109375" customWidth="1"/>
-    <col min="20" max="24" width="8.7109375" customWidth="1"/>
-    <col min="25" max="27" width="10.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="M1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="26"/>
-      <c r="O1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="29" t="s">
-        <v>37</v>
-      </c>
-      <c r="R1" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="S1" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y1" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z1" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA1" s="7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="10">
-        <v>46022</v>
-      </c>
-      <c r="E2" s="5">
-        <v>0</v>
-      </c>
-      <c r="F2" s="5">
-        <v>2.99</v>
-      </c>
-      <c r="G2" s="5">
-        <v>0</v>
-      </c>
-      <c r="H2" s="5">
-        <v>2.99</v>
-      </c>
-      <c r="I2" s="5">
-        <v>0</v>
-      </c>
-      <c r="J2" s="10">
-        <v>46022</v>
-      </c>
-      <c r="K2" s="9">
-        <f>IF(J2&gt;0,J2-D2,"")</f>
-        <v>0</v>
-      </c>
-      <c r="M2" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="N2" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="O2" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="Y2" s="10">
-        <f>B3</f>
-        <v>45899</v>
-      </c>
-      <c r="Z2" s="3">
-        <f>B11*-1</f>
-        <v>-100</v>
-      </c>
-      <c r="AA2" s="3" t="str">
-        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="10">
-        <v>45899</v>
-      </c>
-      <c r="D3" s="10">
-        <v>46112</v>
-      </c>
-      <c r="E3" s="5">
-        <v>0</v>
-      </c>
-      <c r="F3" s="5">
-        <v>2.2200000000000002</v>
-      </c>
-      <c r="G3" s="5">
-        <v>0</v>
-      </c>
-      <c r="H3" s="5">
-        <v>2.2200000000000002</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="10">
-        <v>46112</v>
-      </c>
-      <c r="K3" s="9">
-        <f t="shared" ref="K3:K41" si="0">IF(J3&gt;0,J3-D3,"")</f>
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <f>B11</f>
-        <v>100</v>
-      </c>
-      <c r="N3" s="5">
-        <f>G42</f>
-        <v>0</v>
-      </c>
-      <c r="O3" s="5">
-        <f>F42</f>
-        <v>8.9600000000000009</v>
-      </c>
-      <c r="P3" s="5">
-        <f>H42+I42</f>
-        <v>7.4500000000000011</v>
-      </c>
-      <c r="Q3" s="14" t="str">
-        <f>IF(M3=N3,XIRR(Z2:Z41,Y2:Y41),"")</f>
-        <v/>
-      </c>
-      <c r="R3" s="10" t="str">
-        <f>IF(M3=N3,B14,"")</f>
-        <v/>
-      </c>
-      <c r="S3" s="3" t="str">
-        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v/>
-      </c>
-      <c r="Y3" s="10">
-        <f>J2</f>
-        <v>46022</v>
-      </c>
-      <c r="Z3" s="5">
-        <f>G2+H2+I2</f>
-        <v>2.99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="10">
-        <v>45901</v>
-      </c>
-      <c r="D4" s="10">
-        <v>46203</v>
-      </c>
-      <c r="E4" s="5">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="G4" s="5">
-        <v>0</v>
-      </c>
-      <c r="H4" s="5">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="10">
-        <v>46204</v>
-      </c>
-      <c r="K4" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Y4" s="10">
-        <f t="shared" ref="Y4:Y41" si="1">J3</f>
-        <v>46112</v>
-      </c>
-      <c r="Z4" s="5">
-        <f t="shared" ref="Z4:Z41" si="2">G3+H3+I3</f>
-        <v>2.2200000000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="10">
-        <v>46264</v>
-      </c>
-      <c r="E5" s="5">
-        <v>100</v>
-      </c>
-      <c r="F5" s="5">
-        <v>1.51</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y5" s="10">
-        <f t="shared" si="1"/>
-        <v>46204</v>
-      </c>
-      <c r="Z5" s="5">
-        <f t="shared" si="2"/>
-        <v>2.2400000000000002</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.59</v>
-      </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y6" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z6" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y7" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z7" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="3">
-        <v>12</v>
-      </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y8" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z8" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y9" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z9" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="6">
-        <v>0.09</v>
-      </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y10" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z10" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B11" s="5">
-        <v>100</v>
-      </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y11" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z11" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="10">
-        <v>46264</v>
-      </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y12" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z12" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="9">
-        <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>27</v>
-      </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y13" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z13" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="10"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y14" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z14" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B15" s="3" t="str">
-        <f>IF(M3=N3,B14-B12,"")</f>
-        <v/>
-      </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y15" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z15" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D16" s="7"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y16" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z16" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D17" s="7"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y17" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z17" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D18" s="7"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y18" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z18" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D19" s="7"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y19" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z19" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D20" s="7"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y20" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z20" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D21" s="7"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y21" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z21" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D22" s="7"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y22" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z22" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D23" s="7"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y23" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z23" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D24" s="7"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y24" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z24" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D25" s="7"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y25" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z25" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D26" s="7"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y26" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z26" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D27" s="7"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y27" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z27" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D28" s="7"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y28" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z28" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D29" s="7"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y29" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z29" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D30" s="7"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y30" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z30" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D31" s="7"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y31" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z31" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D32" s="7"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y32" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z32" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D33" s="7"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y33" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z33" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D34" s="7"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y34" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z34" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D35" s="7"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y35" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z35" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D36" s="7"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y36" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z36" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D37" s="7"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="3"/>
-      <c r="K37" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y37" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z37" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D38" s="7"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="3"/>
-      <c r="K38" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y38" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z38" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D39" s="7"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y39" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z39" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D40" s="7"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y40" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z40" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D41" s="7"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y41" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z41" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D42" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="5">
-        <f>SUM(E2:E41)</f>
-        <v>100</v>
-      </c>
-      <c r="F42" s="5">
-        <f t="shared" ref="F42:I42" si="3">SUM(F2:F41)</f>
-        <v>8.9600000000000009</v>
-      </c>
-      <c r="G42" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H42" s="5">
-        <f t="shared" si="3"/>
-        <v>7.4500000000000011</v>
-      </c>
-      <c r="I42" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="R1:R2"/>
-    <mergeCell ref="S1:S2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>$AA$2="+"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
-      <formula>$M$3=$N$3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S3">
-    <cfRule type="expression" dxfId="1" priority="7">
-      <formula>$AA$2="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA2">
-    <cfRule type="expression" dxfId="0" priority="8">
+    <cfRule type="expression" dxfId="6" priority="10">
       <formula>$AA$2="+"</formula>
     </cfRule>
   </conditionalFormatting>
